--- a/prac/2025/Data_Biodiversity2_withdensiometer.xlsx
+++ b/prac/2025/Data_Biodiversity2_withdensiometer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasper/GIT/BIO3018F/prac/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5581D57-2F64-E54F-8841-E3C62F8B079E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F76C73A-5DC5-D14B-B2CF-244B7F8F015F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="10560" activeTab="1" xr2:uid="{8533E4D5-6462-294A-885A-9A5B3288A946}"/>
+    <workbookView xWindow="36620" yWindow="920" windowWidth="19420" windowHeight="10560" activeTab="1" xr2:uid="{8533E4D5-6462-294A-885A-9A5B3288A946}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0C4254F6-ED2B-114D-883F-93AB5D678661}</author>
+    <author>tc={8FA44F95-9FD1-9646-806C-AD5C31EF2D20}</author>
+    <author>tc={A7515A93-97E0-2E4B-B2A1-AB3B60C527B7}</author>
+  </authors>
+  <commentList>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{0C4254F6-ED2B-114D-883F-93AB5D678661}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I made this up…</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{8FA44F95-9FD1-9646-806C-AD5C31EF2D20}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I made this up…</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="2" shapeId="0" xr:uid="{A7515A93-97E0-2E4B-B2A1-AB3B60C527B7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I made this up…</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="184">
   <si>
     <t>Site</t>
   </si>
@@ -73,9 +109,6 @@
     <t>A2</t>
   </si>
   <si>
-    <t>Helichrysum rosum</t>
-  </si>
-  <si>
     <t>Dicerothamnus rhinocerotis</t>
   </si>
   <si>
@@ -94,9 +127,6 @@
     <t xml:space="preserve">Long grass 2 </t>
   </si>
   <si>
-    <t>Ehrhirta calycina/Long grass 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Not grass </t>
   </si>
   <si>
@@ -175,45 +205,21 @@
     <t>Phylica</t>
   </si>
   <si>
-    <t>Diasporus</t>
-  </si>
-  <si>
-    <t>Derdenaia viscosa</t>
-  </si>
-  <si>
-    <t>Perdilaria</t>
-  </si>
-  <si>
     <t>Searsia 1</t>
   </si>
   <si>
     <t>Metalasia</t>
   </si>
   <si>
-    <t xml:space="preserve">Anthespermum </t>
-  </si>
-  <si>
     <t>Protea repens</t>
   </si>
   <si>
-    <t>Hypodisus</t>
-  </si>
-  <si>
     <t>Staberoa multispicula</t>
   </si>
   <si>
-    <t>Restio thaminocorus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seruria </t>
-  </si>
-  <si>
     <t>Dilatris pillansii</t>
   </si>
   <si>
-    <t>Mimetes cuculatis</t>
-  </si>
-  <si>
     <t>Berzelia cordifolia</t>
   </si>
   <si>
@@ -226,15 +232,9 @@
     <t>Protea denticulata</t>
   </si>
   <si>
-    <t>Anthospermum</t>
-  </si>
-  <si>
     <t xml:space="preserve">Erica globularis </t>
   </si>
   <si>
-    <t>Masterceli digitata</t>
-  </si>
-  <si>
     <t>Struthiola</t>
   </si>
   <si>
@@ -244,15 +244,9 @@
     <t>Erica hispidula</t>
   </si>
   <si>
-    <t xml:space="preserve">Leucospermum truncatulum </t>
-  </si>
-  <si>
     <t>Leucadendron salignum</t>
   </si>
   <si>
-    <t>Staberoa 2</t>
-  </si>
-  <si>
     <t>Thamnocortus pellucidus</t>
   </si>
   <si>
@@ -280,9 +274,6 @@
     <t xml:space="preserve">Phylica ericoides </t>
   </si>
   <si>
-    <t>Chrysanthemoides</t>
-  </si>
-  <si>
     <t>Acacia pycnantha</t>
   </si>
   <si>
@@ -301,18 +292,12 @@
     <t>Eucalyptus cinerea</t>
   </si>
   <si>
-    <t>Leucospermum 2</t>
-  </si>
-  <si>
     <t>Phylica 2</t>
   </si>
   <si>
     <t>Berzelia 2</t>
   </si>
   <si>
-    <t>Clifortia 2</t>
-  </si>
-  <si>
     <t>moss</t>
   </si>
   <si>
@@ -337,9 +322,6 @@
     <t>Pteridium aquilli</t>
   </si>
   <si>
-    <t>Pennae mucronata</t>
-  </si>
-  <si>
     <t>vine</t>
   </si>
   <si>
@@ -463,12 +445,6 @@
     <t>Fynbos near Potberg</t>
   </si>
   <si>
-    <t>Older Fynbos</t>
-  </si>
-  <si>
-    <t>Younger Fynbos</t>
-  </si>
-  <si>
     <t>Gazania</t>
   </si>
   <si>
@@ -484,21 +460,12 @@
     <t>Renosterveld2</t>
   </si>
   <si>
-    <t>Base of limestone hills1</t>
-  </si>
-  <si>
-    <t>Base of limestone hills2</t>
-  </si>
-  <si>
     <t>Serotiny</t>
   </si>
   <si>
     <t>Bare Soil</t>
   </si>
   <si>
-    <t>Protea nerifolia</t>
-  </si>
-  <si>
     <t>Pelargonium myrifolium</t>
   </si>
   <si>
@@ -560,13 +527,112 @@
   </si>
   <si>
     <t>Rapenea melanophloeos</t>
+  </si>
+  <si>
+    <t>Helichrysum roseum</t>
+  </si>
+  <si>
+    <t>Ehrharta calycina</t>
+  </si>
+  <si>
+    <t>Osteospermum monoliferum</t>
+  </si>
+  <si>
+    <t>Dodonea viscosa</t>
+  </si>
+  <si>
+    <t>Podylaria</t>
+  </si>
+  <si>
+    <t>Protea neriifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthospermum </t>
+  </si>
+  <si>
+    <t>Hypodiscus aristata</t>
+  </si>
+  <si>
+    <t>Thamnocortus</t>
+  </si>
+  <si>
+    <t>Masterciella digitata</t>
+  </si>
+  <si>
+    <t>Mimetes cuculatus</t>
+  </si>
+  <si>
+    <t>Cliffortia 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leucospermum truncatum </t>
+  </si>
+  <si>
+    <t>Staberoha 2</t>
+  </si>
+  <si>
+    <t>Shale</t>
+  </si>
+  <si>
+    <t>Sand</t>
+  </si>
+  <si>
+    <t>Sandstone</t>
+  </si>
+  <si>
+    <t>Older Sandstone Fynbos</t>
+  </si>
+  <si>
+    <t>Older Sand Fynbos</t>
+  </si>
+  <si>
+    <t>Younger Sand Fynbos</t>
+  </si>
+  <si>
+    <t>Limestone</t>
+  </si>
+  <si>
+    <t>Soil Moisture</t>
+  </si>
+  <si>
+    <t>Base of limestone hills</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Site Code</t>
+  </si>
+  <si>
+    <t>parasite</t>
+  </si>
+  <si>
+    <t>geophyte</t>
+  </si>
+  <si>
+    <t>herb</t>
+  </si>
+  <si>
+    <t>Penaea mucronata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serruria </t>
+  </si>
+  <si>
+    <t>Diospyros dichrophylla</t>
+  </si>
+  <si>
+    <t>Leucospermum calligerum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -591,6 +657,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -739,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -756,6 +834,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,6 +850,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Jasper Slingsby" id="{F2D060D1-1CC5-0A4F-A708-CE3E91C5C79D}" userId="S::01404734@wf.uct.ac.za::8e149e32-6396-4776-90d8-dfbc10c7662b" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1088,1089 +1173,1302 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F5" dT="2025-03-06T10:41:05.67" personId="{F2D060D1-1CC5-0A4F-A708-CE3E91C5C79D}" id="{0C4254F6-ED2B-114D-883F-93AB5D678661}">
+    <text>I made this up…</text>
+  </threadedComment>
+  <threadedComment ref="F12" dT="2025-03-06T10:42:11.81" personId="{F2D060D1-1CC5-0A4F-A708-CE3E91C5C79D}" id="{8FA44F95-9FD1-9646-806C-AD5C31EF2D20}">
+    <text>I made this up…</text>
+  </threadedComment>
+  <threadedComment ref="F13" dT="2025-03-06T10:42:23.13" personId="{F2D060D1-1CC5-0A4F-A708-CE3E91C5C79D}" id="{A7515A93-97E0-2E4B-B2A1-AB3B60C527B7}">
+    <text>I made this up…</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BD7D13-0139-0243-BBB0-EA8D3B16373D}">
-  <dimension ref="A1:H13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9BD7D13-0139-0243-BBB0-EA8D3B16373D}">
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="B1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
       </c>
       <c r="F1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
-        <v>151</v>
-      </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>129</v>
+      </c>
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" t="s">
+        <v>175</v>
+      </c>
+      <c r="L1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0</v>
+      <c r="E2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.11048275</v>
       </c>
       <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>-34.373611111099997</v>
+      </c>
+      <c r="K2">
+        <v>20.52</v>
+      </c>
+      <c r="L2" t="str">
+        <f t="shared" ref="L2:L13" si="0">_xlfn.CONCAT(B2," (",A2,")")</f>
+        <v>Renosterveld1 (A1)</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="E3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="16">
+        <v>0.12313678</v>
+      </c>
+      <c r="G3">
         <v>4.16</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="16">
+        <v>-34.373890000000003</v>
+      </c>
+      <c r="K3" s="16">
+        <v>20.517219999999998</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" si="0"/>
+        <v>Renosterveld2 (A2)</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="E4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.18407319999999999</v>
       </c>
       <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>15</v>
       </c>
-      <c r="H4" t="s">
-        <v>28</v>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4">
+        <v>-34.373888888899998</v>
+      </c>
+      <c r="K4">
+        <v>20.518333333299999</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>Salt marsh (B)</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="F5">
+      <c r="E5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0.21</v>
+      </c>
+      <c r="G5">
         <f>(86+100+39+0)/4</f>
         <v>56.25</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5">
+        <v>-34.380000000000003</v>
+      </c>
+      <c r="K5">
+        <v>20.5333333333</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>Potberg lawn (C)</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="E6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="16">
+        <v>5.8956769999999999E-2</v>
+      </c>
+      <c r="G6">
         <v>6.5</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="H6" t="s">
-        <v>38</v>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>-34.3786111111</v>
+      </c>
+      <c r="K6">
+        <v>20.530833333299999</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>Fynbos near Potberg (D)</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="E7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="16">
+        <v>0.25182136999999999</v>
+      </c>
+      <c r="G7">
         <v>68.900000000000006</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>20</v>
       </c>
-      <c r="H7" t="s">
-        <v>38</v>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7">
+        <v>-34.384722222199997</v>
+      </c>
+      <c r="K7">
+        <v>20.5491666667</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>Older Sandstone Fynbos (E)</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="E8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="16">
+        <v>5.2807890000000003E-2</v>
+      </c>
+      <c r="G8">
         <v>7.54</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8">
+        <v>-34.4005555556</v>
+      </c>
+      <c r="K8">
+        <v>20.556388888899999</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>Older Sand Fynbos (F)</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="16">
+        <v>5.876199E-2</v>
+      </c>
+      <c r="G9">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9">
+        <v>-34.405277777800002</v>
+      </c>
+      <c r="K9">
+        <v>20.561944444400002</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>Younger Sand Fynbos (G)</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="16">
+        <v>4.2834249999999997E-2</v>
+      </c>
+      <c r="G10">
+        <v>0.78</v>
+      </c>
+      <c r="H10">
+        <v>25</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="16">
+        <v>-34.414720000000003</v>
+      </c>
+      <c r="K10">
+        <v>20.5730555556</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>Base of limestone hills (H)</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.38602898000000002</v>
+      </c>
+      <c r="G11">
+        <v>82.68</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="16">
+        <v>-34.41722</v>
+      </c>
+      <c r="K11" s="16">
+        <v>20.635829999999999</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>Alien forest (I)</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
         <v>38</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="G12">
+        <v>72</v>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="16">
+        <v>-34.423650000000002</v>
+      </c>
+      <c r="K12" s="16">
+        <v>20.411799999999999</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>Limestone Fynbos (J)</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>9.6199999999999992</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0.78</v>
-      </c>
-      <c r="G10">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>82.68</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>72</v>
-      </c>
-      <c r="G12">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
       <c r="D13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>5</v>
+      <c r="E13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.15</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="s">
-        <v>28</v>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="16">
+        <v>-34.453150000000001</v>
+      </c>
+      <c r="K13" s="16">
+        <v>20.42503</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>Bush clumps (K)</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73CC6E9-3481-DA47-935F-1274FD90430E}">
-  <dimension ref="A1:EF22"/>
+  <dimension ref="A1:EE22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:136" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:135" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V1" t="s">
+        <v>183</v>
+      </c>
+      <c r="W1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>161</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>145</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>144</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>162</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>164</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>141</v>
+      </c>
+      <c r="BV1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N1" t="s">
-        <v>172</v>
-      </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="BW1" t="s">
+        <v>140</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>139</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>63</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>64</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>65</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>71</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>70</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>66</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>138</v>
+      </c>
+      <c r="CG1" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>103</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>137</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>44</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>136</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>106</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>107</v>
+      </c>
+      <c r="CU1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="CV1" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>135</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>109</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>110</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>134</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>133</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DC1" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DE1" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>123</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>130</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DK1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="DL1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="DM1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="DN1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="DO1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="DP1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="R1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" t="s">
-        <v>43</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="DQ1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="DR1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="DS1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="DT1" s="6"/>
+      <c r="DU1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="DV1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="W1" t="s">
+      <c r="DW1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="X1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="DX1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="DY1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="DZ1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="EA1" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="EB1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="EC1" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:135" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Z1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>168</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>167</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>166</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>90</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>82</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BS1" t="s">
+      <c r="AA2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BT1" t="s">
-        <v>83</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>165</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>20</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>163</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CA1" t="s">
+      <c r="AI2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BE2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BI2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BO2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BP2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="BT2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BU2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BX2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="BY2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BZ2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="CB2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CC2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CD2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CE2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CF2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="CG2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CG1" t="s">
-        <v>161</v>
-      </c>
-      <c r="CH1" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>116</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>117</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>118</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>119</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>120</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>121</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>160</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>49</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>123</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>159</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>124</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>125</v>
-      </c>
-      <c r="CV1" t="s">
-        <v>25</v>
-      </c>
-      <c r="CW1" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>158</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>127</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>128</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>157</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>156</v>
-      </c>
-      <c r="DC1" t="s">
-        <v>129</v>
-      </c>
-      <c r="DD1" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>130</v>
-      </c>
-      <c r="DF1" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>131</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>132</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>143</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>153</v>
-      </c>
-      <c r="DK1" t="s">
-        <v>133</v>
-      </c>
-      <c r="DL1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="DM1" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="DN1" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="DO1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="DP1" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="DQ1" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="DR1" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="DS1" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="DT1" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="DU1" s="6"/>
-      <c r="DV1" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="DW1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="DX1" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="DY1" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="DZ1" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="EA1" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="EB1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="EC1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="ED1" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:136" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BU2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BW2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BX2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="BY2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="BZ2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CA2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="CC2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CD2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CE2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CF2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CG2" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="CH2" s="8" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="CI2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CJ2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CK2" s="8" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="CL2" s="8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="CM2" s="8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="CN2" s="8" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="CO2" s="8" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="CP2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CQ2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CR2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CS2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CT2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CU2" s="8" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="CV2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CW2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CX2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="CY2" s="8" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="CZ2" s="8" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="DA2" s="8" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="DB2" s="8" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="DC2" s="8" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="DD2" s="8" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="DE2" s="8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="DF2" s="8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="DG2" s="8" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="DH2" s="8" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="DI2" s="8" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="DJ2" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="DK2" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="DL2" s="9"/>
-      <c r="DM2" s="7"/>
+        <v>179</v>
+      </c>
+      <c r="DK2" s="9"/>
+      <c r="DL2" s="7"/>
+      <c r="DM2" s="8"/>
       <c r="DN2" s="8"/>
       <c r="DO2" s="8"/>
       <c r="DP2" s="8"/>
       <c r="DQ2" s="8"/>
       <c r="DR2" s="8"/>
       <c r="DS2" s="8"/>
-      <c r="DT2" s="8"/>
-      <c r="DV2" s="11"/>
-      <c r="ED2" s="4"/>
+      <c r="DU2" s="11"/>
+      <c r="EC2" s="4"/>
     </row>
-    <row r="3" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -2202,83 +2500,83 @@
       <c r="J3">
         <v>4</v>
       </c>
-      <c r="DL3" s="4">
-        <f t="shared" ref="DL3:DL12" si="0">SUM(B3:CG3)</f>
+      <c r="DK3" s="4">
+        <f t="shared" ref="DK3:DK12" si="0">SUM(B3:CF3)</f>
         <v>91.133333333333326</v>
       </c>
-      <c r="DM3" s="11">
-        <f>SUMIF(B2:CG2, DM1, B3:CG3)</f>
-        <v>54</v>
+      <c r="DL3" s="11">
+        <f>SUMIF(B2:CF2, DL1, B3:CF3)</f>
+        <v>53</v>
+      </c>
+      <c r="DM3">
+        <f>SUMIF(B2:CF2, DM1, B3:CF3)</f>
+        <v>0</v>
       </c>
       <c r="DN3">
-        <f>SUMIF(B2:CG2, DN1, B3:CG3)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B3:CF3)</f>
+        <v>35</v>
       </c>
       <c r="DO3">
-        <f>SUMIF(B2:CG2, DO1, B3:CG3)</f>
-        <v>35</v>
+        <f>SUMIF(B2:CF2, DO1, B3:CF3)</f>
+        <v>0</v>
       </c>
       <c r="DP3">
-        <f>SUMIF(B2:CG2, DP1, B3:CG3)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DP1, B3:CF3)</f>
+        <v>2.1333333333333333</v>
       </c>
       <c r="DQ3">
-        <f>SUMIF(B2:CG2, DQ1, B3:CG3)</f>
+        <f>SUMIF(G2:DO2, DQ1, B3:DO3)</f>
+        <v>0</v>
+      </c>
+      <c r="DR3">
+        <f>SUMIF(H2:DP2, DR1, B3:DP3)</f>
         <v>2.1333333333333333</v>
       </c>
-      <c r="DR3">
-        <f>SUMIF(G2:DP2, DR1, B3:DP3)</f>
-        <v>0</v>
-      </c>
       <c r="DS3">
-        <f>SUMIF(H2:DQ2, DS1, B3:DQ3)</f>
         <v>0</v>
       </c>
       <c r="DT3">
-        <v>0</v>
-      </c>
-      <c r="DU3">
-        <f>SUM(DM3:DT3)</f>
-        <v>91.13333333333334</v>
-      </c>
-      <c r="DV3" s="10">
-        <f t="shared" ref="DV3:DV14" si="1">DM3/DL3</f>
-        <v>0.59253840526700807</v>
+        <f>SUM(DL3:DS3)</f>
+        <v>92.26666666666668</v>
+      </c>
+      <c r="DU3" s="10">
+        <f t="shared" ref="DU3:DU14" si="1">DL3/DK3</f>
+        <v>0.5815654718361376</v>
+      </c>
+      <c r="DV3" s="6">
+        <f t="shared" ref="DV3:DV14" si="2">DM3/DK3</f>
+        <v>0</v>
       </c>
       <c r="DW3" s="6">
-        <f t="shared" ref="DW3:DW14" si="2">DN3/DL3</f>
-        <v>0</v>
+        <f t="shared" ref="DW3:DW14" si="3">DN3/DK3</f>
+        <v>0.38405267008046823</v>
       </c>
       <c r="DX3" s="6">
-        <f t="shared" ref="DX3:DX14" si="3">DO3/DL3</f>
-        <v>0.38405267008046823</v>
+        <f t="shared" ref="DX3:DX14" si="4">DO3/DK3</f>
+        <v>0</v>
       </c>
       <c r="DY3" s="6">
-        <f t="shared" ref="DY3:DY14" si="4">DP3/DL3</f>
-        <v>0</v>
+        <f t="shared" ref="DY3:DY12" si="5">DP3/DK3</f>
+        <v>2.3408924652523776E-2</v>
       </c>
       <c r="DZ3" s="6">
-        <f t="shared" ref="DZ3:DZ12" si="5">DQ3/DL3</f>
+        <f t="shared" ref="DZ3:DZ12" si="6">DQ3/DK3</f>
+        <v>0</v>
+      </c>
+      <c r="EA3" s="6">
+        <f t="shared" ref="EA3:EA12" si="7">DR3/DK3</f>
         <v>2.3408924652523776E-2</v>
       </c>
-      <c r="EA3" s="6">
-        <f t="shared" ref="EA3:EA12" si="6">DR3/DL3</f>
-        <v>0</v>
-      </c>
       <c r="EB3" s="6">
-        <f t="shared" ref="EB3:EB12" si="7">DS3/DL3</f>
-        <v>0</v>
-      </c>
-      <c r="EC3" s="6">
-        <f t="shared" ref="EC3:EC12" si="8">DT3/DL3</f>
-        <v>0</v>
-      </c>
-      <c r="ED3" s="3">
-        <f>SUM(DV3:EC3)</f>
-        <v>1</v>
+        <f t="shared" ref="EB3:EB12" si="8">DS3/DK3</f>
+        <v>0</v>
+      </c>
+      <c r="EC3" s="3">
+        <f>SUM(DU3:EB3)</f>
+        <v>1.0124359912216534</v>
       </c>
     </row>
-    <row r="4" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2294,83 +2592,83 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="DL4" s="4">
+      <c r="DK4" s="4">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="DM4" s="11">
-        <f>SUMIF(B2:CG2, DM1, B4:CG4)</f>
+      <c r="DL4" s="11">
+        <f>SUMIF(B2:CF2, DL1, B4:CF4)</f>
         <v>65</v>
       </c>
+      <c r="DM4">
+        <f>SUMIF(B2:CF2, DM1, B4:CF4)</f>
+        <v>0</v>
+      </c>
       <c r="DN4">
-        <f>SUMIF(B2:CG2, DN1, B4:CG4)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B4:CF4)</f>
+        <v>1</v>
       </c>
       <c r="DO4">
-        <f>SUMIF(B2:CG2, DO1, B4:CG4)</f>
-        <v>1</v>
+        <f>SUMIF(B2:CF2, DO1, B4:CF4)</f>
+        <v>0</v>
       </c>
       <c r="DP4">
-        <f>SUMIF(B2:CG2, DP1, B4:CG4)</f>
+        <f>SUMIF(B2:CF2, DP1, B4:CF4)</f>
         <v>0</v>
       </c>
       <c r="DQ4">
-        <f>SUMIF(B2:CG2, DQ1, B4:CG4)</f>
+        <f>SUMIF(B2:CF2, DQ1, B4:CF4)</f>
         <v>0</v>
       </c>
       <c r="DR4">
-        <f>SUMIF(B2:CG2, DR1, B4:CG4)</f>
+        <f>SUMIF(B2:CF2, DR1, B4:CF4)</f>
         <v>0</v>
       </c>
       <c r="DS4">
-        <f>SUMIF(B2:CG2, DS1, B4:CG4)</f>
         <v>0</v>
       </c>
       <c r="DT4">
-        <v>0</v>
-      </c>
-      <c r="DU4">
-        <f>SUM(DM4:DT4)</f>
+        <f>SUM(DL4:DS4)</f>
         <v>66</v>
       </c>
-      <c r="DV4" s="11">
+      <c r="DU4" s="11">
         <f t="shared" si="1"/>
         <v>0.98484848484848486</v>
       </c>
+      <c r="DV4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="DW4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX4">
         <f t="shared" si="3"/>
         <v>1.5151515151515152E-2</v>
       </c>
+      <c r="DX4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DY4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED4" s="4">
-        <f t="shared" ref="ED4:ED14" si="9">SUM(DV4:EC4)</f>
+      <c r="EC4" s="4">
+        <f t="shared" ref="EC4:EC14" si="9">SUM(DU4:EB4)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -2378,83 +2676,83 @@
         <f>(16000*0.9)/400</f>
         <v>36</v>
       </c>
-      <c r="DL5" s="4">
+      <c r="DK5" s="4">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="DM5" s="11">
-        <f>SUMIF(B2:CG2, DM1, B5:CG5)</f>
+      <c r="DL5" s="11">
+        <f>SUMIF(B2:CF2, DL1, B5:CF5)</f>
+        <v>0</v>
+      </c>
+      <c r="DM5">
+        <f>SUMIF(B2:CF2, DM1, B5:CF5)</f>
+        <v>0</v>
+      </c>
+      <c r="DN5">
+        <f>SUMIF(D2:DL2, DN1, D5:DL5)</f>
+        <v>0</v>
+      </c>
+      <c r="DO5">
+        <f>SUMIF(B2:CF2, DO1, B5:CF5)</f>
+        <v>0</v>
+      </c>
+      <c r="DP5">
+        <f>SUMIF(F2:DN2, DP1, F5:DN5)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ5">
+        <f>SUMIF(B2:CF2, DQ1, B5:CF5)</f>
+        <v>0</v>
+      </c>
+      <c r="DR5">
+        <f>SUMIF(H2:DP2, DR1, H5:DP5)</f>
         <v>36</v>
       </c>
-      <c r="DN5">
-        <f>SUMIF(B2:CG2, DN1, B5:CG5)</f>
-        <v>0</v>
-      </c>
-      <c r="DO5">
-        <f>SUMIF(D2:DM2, DO1, D5:DM5)</f>
-        <v>0</v>
-      </c>
-      <c r="DP5">
-        <f>SUMIF(B2:CG2, DP1, B5:CG5)</f>
-        <v>0</v>
-      </c>
-      <c r="DQ5">
-        <f>SUMIF(F2:DO2, DQ1, F5:DO5)</f>
-        <v>0</v>
-      </c>
-      <c r="DR5">
-        <f>SUMIF(B2:CG2, DR1, B5:CG5)</f>
-        <v>0</v>
-      </c>
       <c r="DS5">
-        <f>SUMIF(H2:DQ2, DS1, H5:DQ5)</f>
         <v>0</v>
       </c>
       <c r="DT5">
-        <v>0</v>
-      </c>
-      <c r="DU5">
-        <f t="shared" ref="DU5:DU15" si="10">SUM(DM5:DT5)</f>
+        <f t="shared" ref="DT5:DT15" si="10">SUM(DL5:DS5)</f>
         <v>36</v>
       </c>
-      <c r="DV5" s="11">
+      <c r="DU5" s="11">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="DV5">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="DW5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DX5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="DY5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA5">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="EB5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC5">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED5" s="4">
+      <c r="EC5" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -2482,83 +2780,83 @@
         <f>(16000*0.08)/150</f>
         <v>8.5333333333333332</v>
       </c>
-      <c r="DL6" s="4">
+      <c r="DK6" s="4">
         <f t="shared" si="0"/>
         <v>213.66666666666666</v>
       </c>
-      <c r="DM6" s="11">
-        <f>SUMIF(B2:CG2, DM1, B6:CG6)</f>
-        <v>80</v>
+      <c r="DL6" s="11">
+        <f>SUMIF(B2:CF2, DL1, B6:CF6)</f>
+        <v>79</v>
+      </c>
+      <c r="DM6">
+        <f>SUMIF(B2:CF2, DM1, B6:CF6)</f>
+        <v>0</v>
       </c>
       <c r="DN6">
-        <f>SUMIF(B2:CG2, DN1, B6:CG6)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B6:CF6)</f>
+        <v>106.66666666666667</v>
       </c>
       <c r="DO6">
-        <f>SUMIF(B2:CG2, DO1, B6:CG6)</f>
-        <v>106.66666666666667</v>
+        <f>SUMIF(B2:CF2, DO1, B6:CF6)</f>
+        <v>1</v>
       </c>
       <c r="DP6">
-        <f>SUMIF(B2:CG2, DP1, B6:CG6)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DP1, B6:CF6)</f>
+        <v>27</v>
       </c>
       <c r="DQ6">
-        <f>SUMIF(B2:CG2, DQ1, B6:CG6)</f>
-        <v>27</v>
+        <f>SUMIF(B2:CF2, DQ1, B6:CF6)</f>
+        <v>0</v>
       </c>
       <c r="DR6">
-        <f>SUMIF(B2:CG2, DR1, B6:CG6)</f>
+        <f>SUMIF(B2:CF2, DR1, B6:CF6)</f>
         <v>0</v>
       </c>
       <c r="DS6">
-        <f>SUMIF(B2:CG2, DS1, B6:CG6)</f>
         <v>0</v>
       </c>
       <c r="DT6">
-        <v>0</v>
-      </c>
-      <c r="DU6">
         <f t="shared" si="10"/>
         <v>213.66666666666669</v>
       </c>
-      <c r="DV6" s="11">
+      <c r="DU6" s="11">
         <f t="shared" si="1"/>
-        <v>0.37441497659906398</v>
+        <v>0.36973478939157567</v>
+      </c>
+      <c r="DV6">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="DW6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX6">
         <f t="shared" si="3"/>
         <v>0.49921996879875197</v>
       </c>
+      <c r="DX6">
+        <f t="shared" si="4"/>
+        <v>4.6801872074882997E-3</v>
+      </c>
       <c r="DY6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="DZ6">
         <f t="shared" si="5"/>
         <v>0.12636505460218408</v>
       </c>
+      <c r="DZ6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="EA6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC6">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED6" s="4">
+      <c r="EC6" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
@@ -2568,119 +2866,119 @@
       <c r="AQ7">
         <v>5</v>
       </c>
-      <c r="BG7">
+      <c r="BF7">
         <v>5</v>
       </c>
-      <c r="BJ7">
+      <c r="BI7">
         <v>7</v>
       </c>
+      <c r="BS7">
+        <v>6</v>
+      </c>
       <c r="BT7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU7">
         <v>1</v>
       </c>
       <c r="BV7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BW7">
+        <v>11</v>
+      </c>
+      <c r="BX7">
         <v>2</v>
-      </c>
-      <c r="BX7">
-        <v>11</v>
       </c>
       <c r="BY7">
         <v>2</v>
       </c>
       <c r="BZ7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CA7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CB7">
-        <v>11</v>
-      </c>
-      <c r="CC7">
         <v>17</v>
       </c>
-      <c r="DL7" s="4">
+      <c r="DK7" s="4">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="DM7" s="11">
-        <f>SUMIF(B2:CG2, DM1, B7:CG7)</f>
-        <v>53</v>
+      <c r="DL7" s="11">
+        <f>SUMIF(B2:CF2, DL1, B7:CF7)</f>
+        <v>46</v>
+      </c>
+      <c r="DM7">
+        <f>SUMIF(B2:CF2, DM1, B7:CF7)</f>
+        <v>12</v>
       </c>
       <c r="DN7">
-        <f>SUMIF(B2:CG2, DN1, B7:CG7)</f>
-        <v>2</v>
+        <f>SUMIF(B2:CF2, DN1, B7:CF7)</f>
+        <v>13</v>
       </c>
       <c r="DO7">
-        <f>SUMIF(B2:CG2, DO1, B7:CG7)</f>
-        <v>16</v>
+        <f>SUMIF(B2:CF2, DO1, B7:CF7)</f>
+        <v>0</v>
       </c>
       <c r="DP7">
-        <f>SUMIF(B2:CG2, DP1, B7:CG7)</f>
+        <f>SUMIF(B2:CF2, DP1, B7:CF7)</f>
         <v>0</v>
       </c>
       <c r="DQ7">
-        <f>SUMIF(B2:CG2, DQ1, B7:CG7)</f>
+        <f>SUMIF(B2:CF2, DQ1, B7:CF7)</f>
         <v>0</v>
       </c>
       <c r="DR7">
-        <f>SUMIF(B2:CG2, DR1, B7:CG7)</f>
+        <f>SUMIF(B2:CF2, DR1, B7:CF7)</f>
         <v>0</v>
       </c>
       <c r="DS7">
-        <f>SUMIF(B2:CG2, DS1, B7:CG7)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DT7">
-        <v>6</v>
-      </c>
-      <c r="DU7">
         <f t="shared" si="10"/>
         <v>77</v>
       </c>
-      <c r="DV7" s="11">
+      <c r="DU7" s="11">
         <f t="shared" si="1"/>
-        <v>0.68831168831168832</v>
+        <v>0.59740259740259738</v>
+      </c>
+      <c r="DV7">
+        <f t="shared" si="2"/>
+        <v>0.15584415584415584</v>
       </c>
       <c r="DW7">
-        <f t="shared" si="2"/>
-        <v>2.5974025974025976E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.16883116883116883</v>
       </c>
       <c r="DX7">
-        <f t="shared" si="3"/>
-        <v>0.20779220779220781</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="DY7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC7">
         <f t="shared" si="8"/>
         <v>7.792207792207792E-2</v>
       </c>
-      <c r="ED7" s="4">
+      <c r="EC7" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -2729,83 +3027,83 @@
       <c r="AG8">
         <v>1</v>
       </c>
-      <c r="DL8" s="4">
+      <c r="DK8" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="DM8" s="11">
-        <f>SUMIF(B2:CG2, DM1, B8:CG8)</f>
+      <c r="DL8" s="11">
+        <f>SUMIF(B2:CF2, DL1, B8:CF8)</f>
+        <v>11</v>
+      </c>
+      <c r="DM8">
+        <f>SUMIF(B2:CF2, DM1, B8:CF8)</f>
         <v>17</v>
       </c>
       <c r="DN8">
-        <f>SUMIF(B2:CG2, DN1, B8:CG8)</f>
-        <v>9</v>
+        <f>SUMIF(B2:CF2, DN1, B8:CF8)</f>
+        <v>2</v>
       </c>
       <c r="DO8">
-        <f>SUMIF(B2:CG2, DO1, B8:CG8)</f>
-        <v>6</v>
+        <f>SUMIF(B2:CF2, DO1, B8:CF8)</f>
+        <v>1</v>
       </c>
       <c r="DP8">
-        <f>SUMIF(B2:CG2, DP1, B8:CG8)</f>
+        <f>SUMIF(B2:CF2, DP1, B8:CF8)</f>
         <v>0</v>
       </c>
       <c r="DQ8">
-        <f>SUMIF(B2:CG2, DQ1, B8:CG8)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DQ1, B8:CF8)</f>
+        <v>15</v>
       </c>
       <c r="DR8">
-        <f>SUMIF(B2:CG2, DR1, B8:CG8)</f>
-        <v>15</v>
+        <f>SUMIF(B2:CF2, DR1, B8:CF8)</f>
+        <v>0</v>
       </c>
       <c r="DS8">
-        <f>SUMIF(B2:CG2, DS1, B8:CG8)</f>
         <v>0</v>
       </c>
       <c r="DT8">
-        <v>0</v>
-      </c>
-      <c r="DU8">
         <f t="shared" si="10"/>
-        <v>47</v>
-      </c>
-      <c r="DV8" s="11">
+        <v>46</v>
+      </c>
+      <c r="DU8" s="11">
         <f t="shared" si="1"/>
+        <v>0.23404255319148937</v>
+      </c>
+      <c r="DV8">
+        <f t="shared" si="2"/>
         <v>0.36170212765957449</v>
       </c>
       <c r="DW8">
-        <f t="shared" si="2"/>
-        <v>0.19148936170212766</v>
+        <f t="shared" si="3"/>
+        <v>4.2553191489361701E-2</v>
       </c>
       <c r="DX8">
-        <f t="shared" si="3"/>
-        <v>0.1276595744680851</v>
+        <f t="shared" si="4"/>
+        <v>2.1276595744680851E-2</v>
       </c>
       <c r="DY8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="EA8">
         <f t="shared" si="6"/>
         <v>0.31914893617021278</v>
       </c>
+      <c r="EA8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="EB8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED8" s="4">
+      <c r="EC8" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.97872340425531912</v>
       </c>
     </row>
-    <row r="9" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
@@ -2866,85 +3164,88 @@
       <c r="AY9">
         <v>1</v>
       </c>
-      <c r="DL9" s="4">
+      <c r="DK9" s="4">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="DM9" s="11">
-        <f>SUMIF(B2:CG2, DM1, B9:CG9)</f>
-        <v>46</v>
+      <c r="DL9" s="11">
+        <f>SUMIF(B2:CF2, DL1, B9:CF9)</f>
+        <v>45</v>
+      </c>
+      <c r="DM9">
+        <f>SUMIF(B2:CF2, DM1, B9:CF9)</f>
+        <v>1</v>
       </c>
       <c r="DN9">
-        <f>SUMIF(B2:CG2, DN1, B9:CG9)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B9:CF9)</f>
+        <v>48</v>
       </c>
       <c r="DO9">
-        <f>SUMIF(B2:CG2, DO1, B9:CG9)</f>
-        <v>48</v>
+        <f>SUMIF(B2:CF2, DO1, B9:CF9)</f>
+        <v>0</v>
       </c>
       <c r="DP9">
-        <f>SUMIF(B2:CG2, DP1, B9:CG9)</f>
+        <f>SUMIF(B2:CF2, DP1, B9:CF9)</f>
         <v>0</v>
       </c>
       <c r="DQ9">
-        <f>SUMIF(B2:CG2, DQ1, B9:CG9)</f>
+        <f>SUMIF(B2:CF2, DQ1, B9:CF9)</f>
         <v>0</v>
       </c>
       <c r="DR9">
-        <f>SUMIF(B2:CG2, DR1, B9:CG9)</f>
+        <f>SUMIF(B2:CF2, DR1, B9:CF9)</f>
         <v>0</v>
       </c>
       <c r="DS9">
-        <f>SUMIF(B2:CG2, DS1, B9:CG9)</f>
         <v>0</v>
       </c>
       <c r="DT9">
-        <v>0</v>
-      </c>
-      <c r="DU9">
         <f t="shared" si="10"/>
         <v>94</v>
       </c>
-      <c r="DV9" s="11">
+      <c r="DU9" s="11">
         <f t="shared" si="1"/>
-        <v>0.48936170212765956</v>
+        <v>0.47872340425531917</v>
+      </c>
+      <c r="DV9">
+        <f t="shared" si="2"/>
+        <v>1.0638297872340425E-2</v>
       </c>
       <c r="DW9">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX9">
         <f t="shared" si="3"/>
         <v>0.51063829787234039</v>
       </c>
+      <c r="DX9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DY9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC9">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED9" s="4">
+      <c r="EC9" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="AF10">
+        <v>7</v>
       </c>
       <c r="AI10">
         <v>20</v>
@@ -2953,123 +3254,120 @@
         <v>15</v>
       </c>
       <c r="AZ10">
+        <v>8</v>
+      </c>
+      <c r="BA10">
         <v>7</v>
       </c>
-      <c r="BA10">
-        <v>8</v>
-      </c>
       <c r="BB10">
+        <v>1</v>
+      </c>
+      <c r="BC10">
+        <v>5</v>
+      </c>
+      <c r="BD10">
+        <v>15</v>
+      </c>
+      <c r="BE10">
+        <v>11</v>
+      </c>
+      <c r="BF10">
+        <v>9</v>
+      </c>
+      <c r="BG10">
+        <v>4</v>
+      </c>
+      <c r="BH10">
         <v>7</v>
       </c>
-      <c r="BC10">
-        <v>1</v>
-      </c>
-      <c r="BD10">
-        <v>5</v>
-      </c>
-      <c r="BE10">
-        <v>15</v>
-      </c>
-      <c r="BF10">
-        <v>11</v>
-      </c>
-      <c r="BG10">
-        <v>9</v>
-      </c>
-      <c r="BH10">
-        <v>4</v>
-      </c>
       <c r="BI10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BJ10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK10">
         <v>1</v>
       </c>
-      <c r="BL10">
-        <v>1</v>
-      </c>
-      <c r="DL10" s="4">
+      <c r="DK10" s="4">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="DM10" s="11">
-        <f>SUMIF(B2:CG2, DM1, B10:CG10)</f>
-        <v>61</v>
+      <c r="DL10" s="11">
+        <f>SUMIF(B2:CF2, DL1, B10:CF10)</f>
+        <v>47</v>
+      </c>
+      <c r="DM10">
+        <f>SUMIF(B2:CF2, DM1, B10:CF10)</f>
+        <v>14</v>
       </c>
       <c r="DN10">
-        <f>SUMIF(B2:CG2, DN1, B10:CG10)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B10:CF10)</f>
+        <v>52</v>
       </c>
       <c r="DO10">
-        <f>SUMIF(B2:CG2, DO1, B10:CG10)</f>
-        <v>52</v>
+        <f>SUMIF(B2:CF2, DO1, B10:CF10)</f>
+        <v>0</v>
       </c>
       <c r="DP10">
-        <f>SUMIF(B2:CG2, DP1, B10:CG10)</f>
+        <f>SUMIF(B2:CF2, DP1, B10:CF10)</f>
         <v>0</v>
       </c>
       <c r="DQ10">
-        <f>SUMIF(B2:CG2, DQ1, B10:CG10)</f>
+        <f>SUMIF(B2:CF2, DQ1, B10:CF10)</f>
         <v>0</v>
       </c>
       <c r="DR10">
-        <f>SUMIF(B2:CG2, DR1, B10:CG10)</f>
+        <f>SUMIF(B2:CF2, DR1, B10:CF10)</f>
         <v>0</v>
       </c>
       <c r="DS10">
-        <f>SUMIF(B2:CG2, DS1, B10:CG10)</f>
         <v>0</v>
       </c>
       <c r="DT10">
-        <v>0</v>
-      </c>
-      <c r="DU10">
         <f t="shared" si="10"/>
         <v>113</v>
       </c>
-      <c r="DV10" s="11">
+      <c r="DU10" s="11">
         <f t="shared" si="1"/>
-        <v>0.53982300884955747</v>
+        <v>0.41592920353982299</v>
+      </c>
+      <c r="DV10">
+        <f t="shared" si="2"/>
+        <v>0.12389380530973451</v>
       </c>
       <c r="DW10">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX10">
         <f t="shared" si="3"/>
         <v>0.46017699115044247</v>
       </c>
+      <c r="DX10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DY10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB10">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED10" s="4">
+      <c r="EC10" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -3084,329 +3382,329 @@
       <c r="AM11">
         <v>1</v>
       </c>
+      <c r="BL11">
+        <v>4</v>
+      </c>
       <c r="BM11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN11">
         <v>1</v>
       </c>
       <c r="BO11">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="BQ11">
         <v>1</v>
       </c>
       <c r="BR11">
-        <v>1</v>
-      </c>
-      <c r="BS11">
         <v>15</v>
       </c>
-      <c r="DL11" s="4">
+      <c r="DK11" s="4">
         <f t="shared" si="0"/>
         <v>77.333333333333329</v>
       </c>
-      <c r="DM11" s="11">
-        <f>SUMIF(B2:CG2, DM1, B11:CG11)</f>
-        <v>21</v>
+      <c r="DL11" s="11">
+        <f>SUMIF(B2:CF2, DL1, B11:CF11)</f>
+        <v>20</v>
+      </c>
+      <c r="DM11">
+        <f>SUMIF(B2:CF2, DM1, B11:CF11)</f>
+        <v>0</v>
       </c>
       <c r="DN11">
-        <f>SUMIF(B2:CG2, DN1, B11:CG11)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DN1, B11:CF11)</f>
+        <v>41.333333333333329</v>
       </c>
       <c r="DO11">
-        <f>SUMIF(B2:CG2, DO1, B11:CG11)</f>
-        <v>41.333333333333329</v>
+        <f>SUMIF(B2:CF2, DO1, B11:CF11)</f>
+        <v>0</v>
       </c>
       <c r="DP11">
-        <f>SUMIF(B2:CG2, DP1, B11:CG11)</f>
+        <f>SUMIF(B2:CF2, DP1, B11:CF11)</f>
         <v>0</v>
       </c>
       <c r="DQ11">
-        <f>SUMIF(B2:CG2, DQ1, B11:CG11)</f>
+        <f>SUMIF(B2:CF2, DQ1, B11:CF11)</f>
         <v>0</v>
       </c>
       <c r="DR11">
-        <f>SUMIF(B2:CG2, DR1, B11:CG11)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CF2, DR1, B11:CF11)</f>
+        <v>15</v>
       </c>
       <c r="DS11">
-        <f>SUMIF(B2:CG2, DS1, B11:CG11)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="DT11">
-        <v>0</v>
-      </c>
-      <c r="DU11">
         <f t="shared" si="10"/>
-        <v>77.333333333333329</v>
-      </c>
-      <c r="DV11" s="11">
+        <v>76.333333333333329</v>
+      </c>
+      <c r="DU11" s="11">
         <f t="shared" si="1"/>
-        <v>0.27155172413793105</v>
+        <v>0.25862068965517243</v>
+      </c>
+      <c r="DV11">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="DW11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX11">
         <f t="shared" si="3"/>
         <v>0.53448275862068961</v>
       </c>
+      <c r="DX11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="DY11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DZ11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EB11">
         <f t="shared" si="7"/>
         <v>0.19396551724137931</v>
       </c>
-      <c r="EC11">
+      <c r="EB11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED11" s="4">
+      <c r="EC11" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.98706896551724144</v>
       </c>
     </row>
-    <row r="12" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="CC12">
+        <v>5</v>
       </c>
       <c r="CD12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CE12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CF12">
-        <v>1</v>
-      </c>
-      <c r="CG12">
         <v>2</v>
       </c>
-      <c r="DL12" s="4">
+      <c r="DK12" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="DM12" s="11">
-        <f>SUMIF(B2:CG2, DM1, B12:CG12)</f>
+      <c r="DL12" s="11">
+        <f>SUMIF(B2:CF2, DL1, B12:CF12)</f>
+        <v>0</v>
+      </c>
+      <c r="DM12">
+        <f>SUMIF(B2:CF2, DM1, B12:CF15)</f>
         <v>0</v>
       </c>
       <c r="DN12">
-        <f>SUMIF(B2:CG2, DN1, B12:CG15)</f>
+        <f>SUMIF(B2:CF2, DN1, B12:CF15)</f>
         <v>0</v>
       </c>
       <c r="DO12">
-        <f>SUMIF(B2:CG2, DO1, B12:CG15)</f>
-        <v>2</v>
+        <f>SUMIF(B2:CF2, DO1, B12:CF12)</f>
+        <v>10</v>
       </c>
       <c r="DP12">
-        <f>SUMIF(B2:CG2, DP1, B12:CG12)</f>
+        <f>SUMIF(B2:CF2, DP1, B12:CF15)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ12">
+        <f>SUMIF(B2:CF2, DQ1, B12:CF15)</f>
+        <v>0</v>
+      </c>
+      <c r="DR12">
+        <f>SUMIF(B2:CF2, DR1, B12:CF15)</f>
+        <v>0</v>
+      </c>
+      <c r="DS12">
+        <v>0</v>
+      </c>
+      <c r="DT12">
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="DQ12">
-        <f>SUMIF(B2:CG2, DQ1, B12:CG15)</f>
-        <v>0</v>
-      </c>
-      <c r="DR12">
-        <f>SUMIF(B2:CG2, DR1, B12:CG15)</f>
-        <v>0</v>
-      </c>
-      <c r="DS12">
-        <f>SUMIF(B2:CG2, DS1, B12:CG15)</f>
-        <v>0</v>
-      </c>
-      <c r="DT12">
-        <v>0</v>
-      </c>
-      <c r="DU12">
-        <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="DV12" s="11">
+      <c r="DU12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="DV12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="DW12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DX12">
-        <f t="shared" si="3"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="DY12">
         <f t="shared" si="4"/>
         <v>0.83333333333333337</v>
       </c>
+      <c r="DY12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="DZ12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="EA12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="EB12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EC12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="ED12" s="4">
+      <c r="EC12" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
+      </c>
+      <c r="CG13">
+        <v>8</v>
       </c>
       <c r="CH13">
+        <v>6</v>
+      </c>
+      <c r="CI13">
         <v>8</v>
       </c>
-      <c r="CI13">
-        <v>6</v>
-      </c>
       <c r="CJ13">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="CK13">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="CL13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CM13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="CN13">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="CO13">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="CP13">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="CQ13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CR13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CS13">
         <v>4</v>
       </c>
       <c r="CT13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CU13">
         <v>2</v>
       </c>
       <c r="CV13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CW13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CX13">
-        <v>3</v>
-      </c>
-      <c r="CY13">
         <v>5</v>
       </c>
-      <c r="DL13" s="4">
-        <f>SUM(B13:CZ13)</f>
+      <c r="DK13" s="4">
+        <f>SUM(B13:CY13)</f>
         <v>145</v>
       </c>
+      <c r="DL13">
+        <f>SUMIF(B2:DJ2, DL1, B13:DJ13)</f>
+        <v>86</v>
+      </c>
       <c r="DM13">
-        <f>SUMIF(B2:DK2, DM1, B13:DK13)</f>
-        <v>88</v>
+        <f>SUMIF(B2:DJ2, DM1, B13:DJ13)</f>
+        <v>8</v>
       </c>
       <c r="DN13">
-        <f>SUMIF(B2:DK2, DN1, B13:DK13)</f>
-        <v>0</v>
+        <f>SUMIF(B2:DJ2, DN1, B13:DJ13)</f>
+        <v>49</v>
       </c>
       <c r="DO13">
-        <f>SUMIF(B2:DK2, DO1, B13:DK13)</f>
-        <v>49</v>
+        <f>SUMIF(B2:DJ2, DO1, B13:DJ13)</f>
+        <v>0</v>
       </c>
       <c r="DP13">
-        <f>SUMIF(B2:DK2, DP1, B13:DK13)</f>
-        <v>8</v>
+        <f>SUMIF(B2:DJ2, DP1, B13:DJ13)</f>
+        <v>0</v>
       </c>
       <c r="DQ13">
-        <f>SUMIF(B2:DK2, DQ1, B13:DK13)</f>
+        <f>SUMIF(B2:DJ2, DQ1, B13:DJ13)</f>
         <v>0</v>
       </c>
       <c r="DR13">
-        <f>SUMIF(B2:DK2, DR1, B13:DK13)</f>
         <v>0</v>
       </c>
       <c r="DS13">
         <v>0</v>
       </c>
       <c r="DT13">
-        <v>0</v>
-      </c>
-      <c r="DU13">
         <f t="shared" si="10"/>
-        <v>145</v>
-      </c>
-      <c r="DV13" s="11">
+        <v>143</v>
+      </c>
+      <c r="DU13" s="11">
         <f t="shared" si="1"/>
-        <v>0.60689655172413792</v>
+        <v>0.59310344827586203</v>
+      </c>
+      <c r="DV13">
+        <f t="shared" si="2"/>
+        <v>5.5172413793103448E-2</v>
       </c>
       <c r="DW13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DX13">
         <f t="shared" si="3"/>
         <v>0.33793103448275863</v>
       </c>
-      <c r="DY13" s="11">
+      <c r="DX13" s="11">
         <f t="shared" si="4"/>
-        <v>5.5172413793103448E-2</v>
+        <v>0</v>
+      </c>
+      <c r="DY13">
+        <f t="shared" ref="DY13" si="11">DP13/DN13</f>
+        <v>0</v>
       </c>
       <c r="DZ13">
-        <f t="shared" ref="DZ13" si="11">DQ13/DO13</f>
-        <v>0</v>
-      </c>
-      <c r="EA13">
-        <f t="shared" ref="EA13:EA14" si="12">DR13/DO13</f>
-        <v>0</v>
-      </c>
-      <c r="EB13" s="11">
-        <v>0</v>
-      </c>
-      <c r="EC13">
-        <v>0</v>
-      </c>
-      <c r="ED13" s="4">
+        <f t="shared" ref="DZ13:DZ14" si="12">DQ13/DN13</f>
+        <v>0</v>
+      </c>
+      <c r="EA13" s="11">
+        <v>0</v>
+      </c>
+      <c r="EB13">
+        <v>0</v>
+      </c>
+      <c r="EC13" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0.98620689655172411</v>
       </c>
     </row>
-    <row r="14" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:135" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="Q14">
         <f>(16000*0.3)/150</f>
@@ -3415,123 +3713,123 @@
       <c r="S14">
         <v>2</v>
       </c>
-      <c r="CS14">
+      <c r="CR14">
         <v>6</v>
       </c>
+      <c r="CY14">
+        <v>2</v>
+      </c>
       <c r="CZ14">
+        <v>9</v>
+      </c>
+      <c r="DA14">
         <v>2</v>
       </c>
-      <c r="DA14">
-        <v>9</v>
-      </c>
       <c r="DB14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="DC14">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="DD14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DE14">
-        <v>40</v>
-      </c>
-      <c r="DF14">
         <f>(16000*0.3)/400</f>
         <v>12</v>
       </c>
+      <c r="DF14">
+        <v>15</v>
+      </c>
       <c r="DG14">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="DH14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="DI14">
+        <v>1</v>
+      </c>
+      <c r="DJ14">
+        <v>23</v>
+      </c>
+      <c r="DK14" s="4">
+        <f>SUM(B14:DJ14)</f>
+        <v>175</v>
+      </c>
+      <c r="DL14">
+        <f ca="1">SUMIF(B2:DJ2, DL1, B14:CF14)</f>
+        <v>40</v>
+      </c>
+      <c r="DM14">
+        <f ca="1">SUMIF(B2:DJ2, DM1, B14:CF14)</f>
         <v>5</v>
       </c>
-      <c r="DJ14">
-        <v>1</v>
-      </c>
-      <c r="DK14">
-        <v>23</v>
-      </c>
-      <c r="DL14" s="4">
-        <f>SUM(B14:DK14)</f>
-        <v>175</v>
-      </c>
-      <c r="DM14">
-        <f ca="1">SUMIF(B2:DK2, DM1, B14:CG14)</f>
-        <v>69</v>
-      </c>
       <c r="DN14">
-        <f ca="1">SUMIF(B2:DK2, DN1, B14:CG14)</f>
-        <v>5</v>
+        <f ca="1">SUMIF(B2:DJ2, DN1, B14:CF14)</f>
+        <v>99</v>
       </c>
       <c r="DO14">
-        <f ca="1">SUMIF(B2:DK2, DO1, B14:CG14)</f>
-        <v>99</v>
+        <f ca="1">SUMIF(B2:DJ2, DO1, B14:CF14)</f>
+        <v>2</v>
       </c>
       <c r="DP14">
-        <f ca="1">SUMIF(B2:DK2, DP1, B14:CG14)</f>
-        <v>2</v>
+        <f ca="1">SUMIF(B2:DJ2, DP1, B14:CF14)</f>
+        <v>0</v>
       </c>
       <c r="DQ14">
-        <f ca="1">SUMIF(B2:DK2, DQ1, B14:CG14)</f>
+        <f ca="1">SUMIF(B2:DJ2, DQ1, B14:CF14)</f>
         <v>0</v>
       </c>
       <c r="DR14">
-        <f ca="1">SUMIF(B2:DK2, DR1, B14:CG14)</f>
+        <f ca="1">SUMIF(B2:DJ2, DR1, B14:CF14)</f>
         <v>0</v>
       </c>
       <c r="DS14">
-        <f ca="1">SUMIF(B2:DK2, DS1, B14:CG14)</f>
         <v>0</v>
       </c>
       <c r="DT14">
-        <v>0</v>
-      </c>
-      <c r="DU14">
         <f t="shared" ca="1" si="10"/>
-        <v>175</v>
-      </c>
-      <c r="DV14" s="11">
+        <v>146</v>
+      </c>
+      <c r="DU14" s="11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39428571428571429</v>
-      </c>
-      <c r="DW14">
+        <v>0.22857142857142856</v>
+      </c>
+      <c r="DV14">
         <f t="shared" ca="1" si="2"/>
         <v>2.8571428571428571E-2</v>
       </c>
-      <c r="DX14">
+      <c r="DW14">
         <f t="shared" ca="1" si="3"/>
         <v>0.56571428571428573</v>
       </c>
-      <c r="DY14" s="11">
+      <c r="DX14" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>1.1428571428571429E-2</v>
       </c>
+      <c r="DY14">
+        <f ca="1">DP14/DK14</f>
+        <v>0</v>
+      </c>
       <c r="DZ14">
-        <f ca="1">DQ14/DL14</f>
-        <v>0</v>
-      </c>
-      <c r="EA14">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="EB14" s="11">
-        <v>0</v>
-      </c>
-      <c r="EC14">
-        <v>0</v>
-      </c>
-      <c r="ED14" s="4">
+      <c r="EA14" s="11">
+        <v>0</v>
+      </c>
+      <c r="EB14">
+        <v>0</v>
+      </c>
+      <c r="EC14" s="4">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>0.8342857142857143</v>
       </c>
     </row>
-    <row r="15" spans="1:136" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:135" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1">
         <f>SUM(B3:B14)</f>
@@ -3542,7 +3840,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15:BO15" si="13">SUM(D3:D14)</f>
+        <f t="shared" ref="D15:BN15" si="13">SUM(D3:D14)</f>
         <v>28</v>
       </c>
       <c r="E15" s="1">
@@ -3655,420 +3953,416 @@
       </c>
       <c r="AF15" s="1">
         <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AH15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AI15" s="1">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="AJ15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AK15" s="1">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AL15" s="1">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AO15" s="1">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
-      <c r="AG15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AH15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AI15" s="1">
-        <f t="shared" si="13"/>
-        <v>21</v>
-      </c>
-      <c r="AJ15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AK15" s="1">
-        <f t="shared" si="13"/>
+      <c r="AR15" s="1">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="AS15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AT15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AU15" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AV15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AW15" s="1">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="AX15" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="AY15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="1">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="BA15" s="1">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="BB15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="BD15" s="1">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="BE15" s="1">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="BF15" s="1">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BH15" s="1">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="BI15" s="1">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="BJ15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BK15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BL15" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" ref="BO15:EA15" si="14">SUM(BO3:BO14)</f>
+        <v>14</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="CJ15" s="1">
+        <f t="shared" si="14"/>
+        <v>24</v>
+      </c>
+      <c r="CK15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="CL15" s="1">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="CM15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="14"/>
+        <v>26</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="AL15" s="1">
-        <f t="shared" si="13"/>
-        <v>18</v>
-      </c>
-      <c r="AM15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="AN15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AO15" s="1">
-        <f t="shared" si="13"/>
-        <v>30</v>
-      </c>
-      <c r="AP15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AQ15" s="1">
-        <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
-      <c r="AR15" s="1">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="AS15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AT15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AU15" s="1">
-        <f t="shared" si="13"/>
-        <v>13</v>
-      </c>
-      <c r="AV15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AW15" s="1">
-        <f t="shared" si="13"/>
+      <c r="CX15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AX15" s="1">
-        <f t="shared" si="13"/>
+      <c r="CZ15" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="AY15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AZ15" s="1">
-        <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="BA15" s="1">
-        <f t="shared" si="13"/>
-        <v>8</v>
-      </c>
-      <c r="BB15" s="1">
-        <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="BC15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BD15" s="1">
-        <f t="shared" si="13"/>
+      <c r="DC15" s="1">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="14"/>
+        <v>40</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="DG15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="DH15" s="1">
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="BE15" s="1">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="BF15" s="1">
-        <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="BG15" s="1">
-        <f t="shared" si="13"/>
-        <v>14</v>
-      </c>
-      <c r="BH15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="BI15" s="1">
-        <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="BJ15" s="1">
-        <f t="shared" si="13"/>
-        <v>9</v>
-      </c>
-      <c r="BK15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BL15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BM15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="BN15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BO15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BP15" s="1">
-        <f t="shared" ref="BP15:EB15" si="14">SUM(BP3:BP14)</f>
-        <v>14</v>
-      </c>
-      <c r="BQ15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BR15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BS15" s="1">
-        <f t="shared" si="14"/>
-        <v>15</v>
-      </c>
-      <c r="BT15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="BU15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BV15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BW15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="BX15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="BY15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="BZ15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CA15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CB15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="CC15" s="1">
-        <f t="shared" si="14"/>
-        <v>17</v>
-      </c>
-      <c r="CD15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CE15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CF15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="CG15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CH15" s="1">
-        <f t="shared" si="14"/>
-        <v>8</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="CJ15" s="1">
-        <f t="shared" si="14"/>
-        <v>8</v>
-      </c>
-      <c r="CK15" s="1">
-        <f t="shared" si="14"/>
-        <v>24</v>
-      </c>
-      <c r="CL15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="CM15" s="1">
-        <f t="shared" si="14"/>
-        <v>12</v>
-      </c>
-      <c r="CN15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CO15" s="1">
-        <f t="shared" si="14"/>
-        <v>26</v>
-      </c>
-      <c r="CP15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CQ15" s="1">
-        <f t="shared" si="14"/>
-        <v>13</v>
-      </c>
-      <c r="CR15" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="CS15" s="1">
-        <f t="shared" si="14"/>
-        <v>10</v>
-      </c>
-      <c r="CT15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CU15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CV15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CW15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="CX15" s="1">
-        <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="CY15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="14"/>
-        <v>20</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="14"/>
-        <v>40</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="14"/>
-        <v>12</v>
-      </c>
-      <c r="DG15" s="1">
-        <f t="shared" si="14"/>
-        <v>15</v>
-      </c>
-      <c r="DH15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
       <c r="DI15" s="1">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="DJ15" s="1">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="DK15" s="1">
-        <f t="shared" si="14"/>
         <v>23</v>
       </c>
-      <c r="DL15" s="5">
+      <c r="DK15" s="5">
         <f t="shared" si="14"/>
         <v>1147.1333333333332</v>
+      </c>
+      <c r="DL15" s="1">
+        <f t="shared" ca="1" si="14"/>
+        <v>492</v>
       </c>
       <c r="DM15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>590</v>
+        <v>57</v>
       </c>
       <c r="DN15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>16</v>
+        <v>447</v>
       </c>
       <c r="DO15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>456</v>
+        <v>14</v>
       </c>
       <c r="DP15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>20</v>
+        <v>29.133333333333333</v>
       </c>
       <c r="DQ15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>29.133333333333333</v>
+        <v>15</v>
       </c>
       <c r="DR15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>15</v>
+        <v>53.133333333333333</v>
       </c>
       <c r="DS15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="DT15" s="15">
+        <f t="shared" ca="1" si="10"/>
+        <v>1113.2666666666669</v>
+      </c>
+      <c r="DU15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>15</v>
-      </c>
-      <c r="DT15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="DU15" s="15">
-        <f t="shared" ca="1" si="10"/>
-        <v>1147.1333333333334</v>
+        <v>4.7425420709678905</v>
       </c>
       <c r="DV15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>6.30373438381082</v>
+        <v>0.73582222905033723</v>
       </c>
       <c r="DW15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.24603481624758222</v>
+        <v>3.5187518821917827</v>
       </c>
       <c r="DX15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>3.8094859707982116</v>
+        <v>0.87071868771407401</v>
       </c>
       <c r="DY15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.89993431855500827</v>
+        <v>0.14977397925470787</v>
       </c>
       <c r="DZ15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.14977397925470787</v>
+        <v>0.31914893617021278</v>
       </c>
       <c r="EA15" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.31914893617021278</v>
+        <f t="shared" si="14"/>
+        <v>1.217374441893903</v>
       </c>
       <c r="EB15" s="1">
-        <f t="shared" si="14"/>
-        <v>0.19396551724137931</v>
-      </c>
-      <c r="EC15" s="1">
-        <f t="shared" ref="EC15:ED15" si="15">SUM(EC3:EC14)</f>
+        <f t="shared" ref="EB15:EC15" si="15">SUM(EB3:EB14)</f>
         <v>7.792207792207792E-2</v>
       </c>
-      <c r="ED15" s="15">
+      <c r="EC15" s="15">
         <f t="shared" ca="1" si="15"/>
-        <v>12</v>
-      </c>
+        <v>11.632054305164987</v>
+      </c>
+      <c r="ED15"/>
       <c r="EE15"/>
-      <c r="EF15"/>
     </row>
-    <row r="16" spans="1:136" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:135" x14ac:dyDescent="0.2">
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="H16" s="12"/>
@@ -4101,23 +4395,22 @@
       <c r="AW16" s="12"/>
       <c r="AX16" s="12"/>
       <c r="AY16" s="12"/>
-      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
       <c r="BB16" s="12"/>
       <c r="BC16" s="12"/>
       <c r="BD16" s="12"/>
       <c r="BE16" s="12"/>
-      <c r="BF16" s="12"/>
-      <c r="BH16" s="12"/>
-      <c r="BJ16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BI16" s="12"/>
+      <c r="BK16" s="12"/>
       <c r="BL16" s="12"/>
       <c r="BM16" s="12"/>
       <c r="BN16" s="12"/>
       <c r="BO16" s="12"/>
       <c r="BP16" s="12"/>
-      <c r="BQ16" s="12"/>
-      <c r="BT16" s="12"/>
-      <c r="BW16" s="12"/>
-      <c r="CB16" s="12"/>
+      <c r="BS16" s="12"/>
+      <c r="BV16" s="12"/>
+      <c r="CA16" s="12"/>
     </row>
     <row r="22" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G22" s="12"/>
@@ -4135,19 +4428,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>31</v>
-      </c>
-      <c r="E1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -4197,7 +4490,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>0.05</v>

--- a/prac/2025/Data_Biodiversity2_withdensiometer.xlsx
+++ b/prac/2025/Data_Biodiversity2_withdensiometer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasper/GIT/BIO3018F/prac/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F76C73A-5DC5-D14B-B2CF-244B7F8F015F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DD1BD7-CA3D-F649-9AFE-C798B5FDA0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36620" yWindow="920" windowWidth="19420" windowHeight="10560" activeTab="1" xr2:uid="{8533E4D5-6462-294A-885A-9A5B3288A946}"/>
+    <workbookView xWindow="39820" yWindow="920" windowWidth="19420" windowHeight="10560" activeTab="1" xr2:uid="{8533E4D5-6462-294A-885A-9A5B3288A946}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="184">
   <si>
     <t>Site</t>
   </si>
@@ -145,9 +145,6 @@
     <t>Cenchrus clandestinum</t>
   </si>
   <si>
-    <t>Thesium spp.</t>
-  </si>
-  <si>
     <t>Dung level</t>
   </si>
   <si>
@@ -214,9 +211,6 @@
     <t>Protea repens</t>
   </si>
   <si>
-    <t>Staberoa multispicula</t>
-  </si>
-  <si>
     <t>Dilatris pillansii</t>
   </si>
   <si>
@@ -292,9 +286,6 @@
     <t>Eucalyptus cinerea</t>
   </si>
   <si>
-    <t>Phylica 2</t>
-  </si>
-  <si>
     <t>Berzelia 2</t>
   </si>
   <si>
@@ -385,9 +376,6 @@
     <t>Thamnochortus</t>
   </si>
   <si>
-    <t>Leucadendron spp.</t>
-  </si>
-  <si>
     <t>Shiny Ateraceae</t>
   </si>
   <si>
@@ -397,9 +385,6 @@
     <t>Spiky Asteraceae</t>
   </si>
   <si>
-    <t>Phylica spp.</t>
-  </si>
-  <si>
     <t>Anthospermum aethiopicum</t>
   </si>
   <si>
@@ -508,9 +493,6 @@
     <t>Serruria nervosa</t>
   </si>
   <si>
-    <t>Leucadendron xanthoconum</t>
-  </si>
-  <si>
     <t>Cliffortia stricta</t>
   </si>
   <si>
@@ -547,9 +529,6 @@
     <t>Protea neriifolia</t>
   </si>
   <si>
-    <t xml:space="preserve">Anthospermum </t>
-  </si>
-  <si>
     <t>Hypodiscus aristata</t>
   </si>
   <si>
@@ -568,9 +547,6 @@
     <t xml:space="preserve">Leucospermum truncatum </t>
   </si>
   <si>
-    <t>Staberoha 2</t>
-  </si>
-  <si>
     <t>Shale</t>
   </si>
   <si>
@@ -626,6 +602,30 @@
   </si>
   <si>
     <t>Leucospermum calligerum</t>
+  </si>
+  <si>
+    <t>Anthospermum galioides</t>
+  </si>
+  <si>
+    <t>Leucadendron xanthoconus</t>
+  </si>
+  <si>
+    <t>Leucadendron muirii</t>
+  </si>
+  <si>
+    <t>Metalasia calcicola</t>
+  </si>
+  <si>
+    <t>Phylica incurvata</t>
+  </si>
+  <si>
+    <t>Staberoha cernua</t>
+  </si>
+  <si>
+    <t>Thesium spp 2</t>
+  </si>
+  <si>
+    <t>Thesium spp 1</t>
   </si>
 </sst>
 </file>
@@ -1198,37 +1198,37 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G1" t="s">
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J1" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="L1" t="s">
         <v>0</v>
@@ -1239,16 +1239,16 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F2" s="16">
         <v>0.11048275</v>
@@ -1260,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>-34.373611111099997</v>
@@ -1278,16 +1278,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F3" s="16">
         <v>0.12313678</v>
@@ -1299,7 +1299,7 @@
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="16">
         <v>-34.373890000000003</v>
@@ -1317,16 +1317,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F4" s="16">
         <v>0.18407319999999999</v>
@@ -1338,7 +1338,7 @@
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4">
         <v>-34.373888888899998</v>
@@ -1356,16 +1356,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F5" s="16">
         <v>0.21</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5">
         <v>-34.380000000000003</v>
@@ -1396,16 +1396,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F6" s="16">
         <v>5.8956769999999999E-2</v>
@@ -1417,7 +1417,7 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>-34.3786111111</v>
@@ -1435,16 +1435,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F7" s="16">
         <v>0.25182136999999999</v>
@@ -1456,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>-34.384722222199997</v>
@@ -1474,16 +1474,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F8" s="16">
         <v>5.2807890000000003E-2</v>
@@ -1495,7 +1495,7 @@
         <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8">
         <v>-34.4005555556</v>
@@ -1510,19 +1510,19 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F9" s="16">
         <v>5.876199E-2</v>
@@ -1534,7 +1534,7 @@
         <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>-34.405277777800002</v>
@@ -1549,19 +1549,19 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F10" s="16">
         <v>4.2834249999999997E-2</v>
@@ -1573,7 +1573,7 @@
         <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J10" s="16">
         <v>-34.414720000000003</v>
@@ -1588,19 +1588,19 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F11" s="16">
         <v>0.38602898000000002</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J11" s="16">
         <v>-34.41722</v>
@@ -1627,19 +1627,19 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F12" s="16">
         <v>0.08</v>
@@ -1651,7 +1651,7 @@
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J12" s="16">
         <v>-34.423650000000002</v>
@@ -1666,19 +1666,19 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F13" s="16">
         <v>0.15</v>
@@ -1690,7 +1690,7 @@
         <v>5</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="16">
         <v>-34.453150000000001</v>
@@ -1711,15 +1711,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D73CC6E9-3481-DA47-935F-1274FD90430E}">
-  <dimension ref="A1:EE22"/>
+  <dimension ref="A1:EC22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:135" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:133" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C1" t="s">
         <v>11</v>
@@ -1737,10 +1737,10 @@
         <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="I1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J1" t="s">
         <v>16</v>
@@ -1752,10 +1752,10 @@
         <v>19</v>
       </c>
       <c r="M1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="N1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O1" t="s">
         <v>20</v>
@@ -1764,711 +1764,699 @@
         <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R1" t="s">
         <v>22</v>
       </c>
       <c r="S1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1" t="s">
         <v>39</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>40</v>
       </c>
-      <c r="U1" t="s">
-        <v>41</v>
-      </c>
       <c r="V1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="W1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="X1" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="Y1" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="Z1" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="AA1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AB1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AC1" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="AD1" t="s">
         <v>43</v>
       </c>
       <c r="AE1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AF1" t="s">
         <v>44</v>
       </c>
-      <c r="AF1" t="s">
-        <v>157</v>
-      </c>
       <c r="AG1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM1" t="s">
         <v>45</v>
       </c>
-      <c r="AH1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AN1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO1" t="s">
         <v>46</v>
       </c>
-      <c r="AJ1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AK1" t="s">
+      <c r="AP1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>177</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>138</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>156</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BH1" t="s">
         <v>181</v>
       </c>
-      <c r="AL1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>145</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>144</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>143</v>
-      </c>
-      <c r="BF1" t="s">
+      <c r="BI1" t="s">
         <v>55</v>
       </c>
-      <c r="BG1" t="s">
-        <v>162</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>163</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>119</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>120</v>
+      </c>
+      <c r="BM1" t="s">
         <v>56</v>
       </c>
-      <c r="BJ1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BK1" t="s">
+      <c r="BN1" t="s">
         <v>57</v>
       </c>
-      <c r="BL1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>125</v>
-      </c>
       <c r="BO1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BP1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BQ1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>136</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BX1" t="s">
         <v>61</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BY1" t="s">
         <v>62</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>142</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>141</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>140</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>139</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>83</v>
       </c>
       <c r="BZ1" t="s">
         <v>63</v>
       </c>
       <c r="CA1" t="s">
+        <v>69</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>68</v>
+      </c>
+      <c r="CC1" t="s">
         <v>64</v>
       </c>
-      <c r="CB1" t="s">
-        <v>65</v>
-      </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
+        <v>133</v>
+      </c>
+      <c r="CE1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>178</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>132</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>179</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>180</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>182</v>
+      </c>
+      <c r="CT1" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>130</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>104</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>105</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>129</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>128</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DA1" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DC1" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="DJ1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="DK1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="DL1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="DM1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="DN1" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>70</v>
-      </c>
-      <c r="CE1" t="s">
-        <v>66</v>
-      </c>
-      <c r="CF1" t="s">
-        <v>138</v>
-      </c>
-      <c r="CG1" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="CH1" t="s">
-        <v>98</v>
-      </c>
-      <c r="CI1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>102</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>103</v>
-      </c>
-      <c r="CN1" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>104</v>
-      </c>
-      <c r="CP1" t="s">
-        <v>44</v>
-      </c>
-      <c r="CQ1" t="s">
-        <v>105</v>
-      </c>
-      <c r="CR1" t="s">
-        <v>136</v>
-      </c>
-      <c r="CS1" t="s">
-        <v>106</v>
-      </c>
-      <c r="CT1" t="s">
-        <v>107</v>
-      </c>
-      <c r="CU1" t="s">
-        <v>23</v>
-      </c>
-      <c r="CV1" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="CW1" t="s">
-        <v>135</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>109</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>110</v>
-      </c>
-      <c r="CZ1" t="s">
-        <v>134</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>133</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>111</v>
-      </c>
-      <c r="DC1" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="DD1" t="s">
-        <v>112</v>
-      </c>
-      <c r="DE1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>113</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>114</v>
-      </c>
-      <c r="DH1" t="s">
-        <v>123</v>
-      </c>
-      <c r="DI1" t="s">
-        <v>130</v>
-      </c>
-      <c r="DJ1" t="s">
-        <v>115</v>
-      </c>
-      <c r="DK1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="DL1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="DM1" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="DN1" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="DO1" s="6" t="s">
         <v>77</v>
       </c>
       <c r="DP1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="DQ1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="DR1" s="6"/>
+      <c r="DS1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="DT1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="DU1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="DV1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="DW1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="DX1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="DY1" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="DZ1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="EA1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="DQ1" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="DR1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="DS1" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="DT1" s="6"/>
-      <c r="DU1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="DV1" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="DW1" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="DX1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="DY1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="DZ1" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="EA1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="EB1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="EC1" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:135" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="N2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="T2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="W2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="AA2" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AK2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AO2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AS2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AL2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="AU2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="AZ2" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="BA2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BF2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="BG2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BH2" s="2" t="s">
-        <v>78</v>
+      <c r="BH2" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BK2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BL2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="BP2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BK2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BQ2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BT2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BU2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BX2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="CA2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CB2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CC2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CD2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="CE2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BO2" s="2" t="s">
+      <c r="CF2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BP2" s="2" t="s">
+      <c r="CG2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CH2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CI2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="CJ2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="CK2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BQ2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BT2" s="1" t="s">
+      <c r="CL2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="CM2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CN2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CO2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CP2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CQ2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CR2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CS2" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="CT2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CU2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CV2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CW2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="CX2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="CY2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BU2" s="1" t="s">
+      <c r="CZ2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="DA2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="DB2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="DC2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="DD2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="DE2" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BV2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="BW2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BX2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BY2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="CB2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="CC2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CD2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CE2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CF2" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="CG2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CH2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CI2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CJ2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CK2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="CL2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="CM2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CN2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="CO2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CP2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CQ2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CR2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CS2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CT2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CU2" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="CV2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CW2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CX2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="CY2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="CZ2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="DA2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="DB2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="DC2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="DD2" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="DE2" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="DF2" s="8" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="DG2" s="8" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="DH2" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="DI2" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="DJ2" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="DK2" s="9"/>
-      <c r="DL2" s="7"/>
+        <v>171</v>
+      </c>
+      <c r="DI2" s="9"/>
+      <c r="DJ2" s="7"/>
+      <c r="DK2" s="8"/>
+      <c r="DL2" s="8"/>
       <c r="DM2" s="8"/>
       <c r="DN2" s="8"/>
       <c r="DO2" s="8"/>
       <c r="DP2" s="8"/>
       <c r="DQ2" s="8"/>
-      <c r="DR2" s="8"/>
-      <c r="DS2" s="8"/>
-      <c r="DU2" s="11"/>
-      <c r="EC2" s="4"/>
+      <c r="DS2" s="11"/>
+      <c r="EA2" s="4"/>
     </row>
-    <row r="3" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
@@ -2500,83 +2488,83 @@
       <c r="J3">
         <v>4</v>
       </c>
-      <c r="DK3" s="4">
-        <f t="shared" ref="DK3:DK12" si="0">SUM(B3:CF3)</f>
+      <c r="DI3" s="4">
+        <f t="shared" ref="DI3:DI12" si="0">SUM(B3:CD3)</f>
         <v>91.133333333333326</v>
       </c>
-      <c r="DL3" s="11">
-        <f>SUMIF(B2:CF2, DL1, B3:CF3)</f>
+      <c r="DJ3" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B3:CD3)</f>
         <v>53</v>
       </c>
+      <c r="DK3">
+        <f>SUMIF(B2:CD2, DK1, B3:CD3)</f>
+        <v>0</v>
+      </c>
+      <c r="DL3">
+        <f>SUMIF(B2:CD2, DL1, B3:CD3)</f>
+        <v>35</v>
+      </c>
       <c r="DM3">
-        <f>SUMIF(B2:CF2, DM1, B3:CF3)</f>
+        <f>SUMIF(B2:CD2, DM1, B3:CD3)</f>
         <v>0</v>
       </c>
       <c r="DN3">
-        <f>SUMIF(B2:CF2, DN1, B3:CF3)</f>
-        <v>35</v>
+        <f>SUMIF(B2:CD2, DN1, B3:CD3)</f>
+        <v>2.1333333333333333</v>
       </c>
       <c r="DO3">
-        <f>SUMIF(B2:CF2, DO1, B3:CF3)</f>
+        <f>SUMIF(G2:DM2, DO1, B3:DM3)</f>
         <v>0</v>
       </c>
       <c r="DP3">
-        <f>SUMIF(B2:CF2, DP1, B3:CF3)</f>
+        <f>SUMIF(H2:DN2, DP1, B3:DN3)</f>
         <v>2.1333333333333333</v>
       </c>
       <c r="DQ3">
-        <f>SUMIF(G2:DO2, DQ1, B3:DO3)</f>
         <v>0</v>
       </c>
       <c r="DR3">
-        <f>SUMIF(H2:DP2, DR1, B3:DP3)</f>
-        <v>2.1333333333333333</v>
-      </c>
-      <c r="DS3">
-        <v>0</v>
-      </c>
-      <c r="DT3">
-        <f>SUM(DL3:DS3)</f>
+        <f>SUM(DJ3:DQ3)</f>
         <v>92.26666666666668</v>
       </c>
-      <c r="DU3" s="10">
-        <f t="shared" ref="DU3:DU14" si="1">DL3/DK3</f>
+      <c r="DS3" s="10">
+        <f t="shared" ref="DS3:DS14" si="1">DJ3/DI3</f>
         <v>0.5815654718361376</v>
       </c>
+      <c r="DT3" s="6">
+        <f t="shared" ref="DT3:DT14" si="2">DK3/DI3</f>
+        <v>0</v>
+      </c>
+      <c r="DU3" s="6">
+        <f t="shared" ref="DU3:DU14" si="3">DL3/DI3</f>
+        <v>0.38405267008046823</v>
+      </c>
       <c r="DV3" s="6">
-        <f t="shared" ref="DV3:DV14" si="2">DM3/DK3</f>
+        <f t="shared" ref="DV3:DV14" si="4">DM3/DI3</f>
         <v>0</v>
       </c>
       <c r="DW3" s="6">
-        <f t="shared" ref="DW3:DW14" si="3">DN3/DK3</f>
-        <v>0.38405267008046823</v>
+        <f t="shared" ref="DW3:DW12" si="5">DN3/DI3</f>
+        <v>2.3408924652523776E-2</v>
       </c>
       <c r="DX3" s="6">
-        <f t="shared" ref="DX3:DX14" si="4">DO3/DK3</f>
+        <f t="shared" ref="DX3:DX12" si="6">DO3/DI3</f>
         <v>0</v>
       </c>
       <c r="DY3" s="6">
-        <f t="shared" ref="DY3:DY12" si="5">DP3/DK3</f>
+        <f t="shared" ref="DY3:DY12" si="7">DP3/DI3</f>
         <v>2.3408924652523776E-2</v>
       </c>
       <c r="DZ3" s="6">
-        <f t="shared" ref="DZ3:DZ12" si="6">DQ3/DK3</f>
-        <v>0</v>
-      </c>
-      <c r="EA3" s="6">
-        <f t="shared" ref="EA3:EA12" si="7">DR3/DK3</f>
-        <v>2.3408924652523776E-2</v>
-      </c>
-      <c r="EB3" s="6">
-        <f t="shared" ref="EB3:EB12" si="8">DS3/DK3</f>
-        <v>0</v>
-      </c>
-      <c r="EC3" s="3">
-        <f>SUM(DU3:EB3)</f>
+        <f t="shared" ref="DZ3:DZ12" si="8">DQ3/DI3</f>
+        <v>0</v>
+      </c>
+      <c r="EA3" s="3">
+        <f>SUM(DS3:DZ3)</f>
         <v>1.0124359912216534</v>
       </c>
     </row>
-    <row r="4" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -2592,83 +2580,83 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="DK4" s="4">
+      <c r="DI4" s="4">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="DL4" s="11">
-        <f>SUMIF(B2:CF2, DL1, B4:CF4)</f>
+      <c r="DJ4" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B4:CD4)</f>
         <v>65</v>
       </c>
+      <c r="DK4">
+        <f>SUMIF(B2:CD2, DK1, B4:CD4)</f>
+        <v>0</v>
+      </c>
+      <c r="DL4">
+        <f>SUMIF(B2:CD2, DL1, B4:CD4)</f>
+        <v>1</v>
+      </c>
       <c r="DM4">
-        <f>SUMIF(B2:CF2, DM1, B4:CF4)</f>
+        <f>SUMIF(B2:CD2, DM1, B4:CD4)</f>
         <v>0</v>
       </c>
       <c r="DN4">
-        <f>SUMIF(B2:CF2, DN1, B4:CF4)</f>
-        <v>1</v>
+        <f>SUMIF(B2:CD2, DN1, B4:CD4)</f>
+        <v>0</v>
       </c>
       <c r="DO4">
-        <f>SUMIF(B2:CF2, DO1, B4:CF4)</f>
+        <f>SUMIF(B2:CD2, DO1, B4:CD4)</f>
         <v>0</v>
       </c>
       <c r="DP4">
-        <f>SUMIF(B2:CF2, DP1, B4:CF4)</f>
+        <f>SUMIF(B2:CD2, DP1, B4:CD4)</f>
         <v>0</v>
       </c>
       <c r="DQ4">
-        <f>SUMIF(B2:CF2, DQ1, B4:CF4)</f>
         <v>0</v>
       </c>
       <c r="DR4">
-        <f>SUMIF(B2:CF2, DR1, B4:CF4)</f>
-        <v>0</v>
-      </c>
-      <c r="DS4">
-        <v>0</v>
-      </c>
-      <c r="DT4">
-        <f>SUM(DL4:DS4)</f>
+        <f>SUM(DJ4:DQ4)</f>
         <v>66</v>
       </c>
-      <c r="DU4" s="11">
+      <c r="DS4" s="11">
         <f t="shared" si="1"/>
         <v>0.98484848484848486</v>
       </c>
-      <c r="DV4">
+      <c r="DT4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="DW4">
+      <c r="DU4">
         <f t="shared" si="3"/>
         <v>1.5151515151515152E-2</v>
       </c>
+      <c r="DV4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="DW4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="DX4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="DY4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="DZ4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EB4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC4" s="4">
-        <f t="shared" ref="EC4:EC14" si="9">SUM(DU4:EB4)</f>
+      <c r="EA4" s="4">
+        <f t="shared" ref="EA4:EA14" si="9">SUM(DS4:DZ4)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -2676,83 +2664,83 @@
         <f>(16000*0.9)/400</f>
         <v>36</v>
       </c>
-      <c r="DK5" s="4">
+      <c r="DI5" s="4">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="DL5" s="11">
-        <f>SUMIF(B2:CF2, DL1, B5:CF5)</f>
+      <c r="DJ5" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B5:CD5)</f>
+        <v>0</v>
+      </c>
+      <c r="DK5">
+        <f>SUMIF(B2:CD2, DK1, B5:CD5)</f>
+        <v>0</v>
+      </c>
+      <c r="DL5">
+        <f>SUMIF(D2:DJ2, DL1, D5:DJ5)</f>
         <v>0</v>
       </c>
       <c r="DM5">
-        <f>SUMIF(B2:CF2, DM1, B5:CF5)</f>
+        <f>SUMIF(B2:CD2, DM1, B5:CD5)</f>
         <v>0</v>
       </c>
       <c r="DN5">
-        <f>SUMIF(D2:DL2, DN1, D5:DL5)</f>
+        <f>SUMIF(F2:DL2, DN1, F5:DL5)</f>
         <v>0</v>
       </c>
       <c r="DO5">
-        <f>SUMIF(B2:CF2, DO1, B5:CF5)</f>
+        <f>SUMIF(B2:CD2, DO1, B5:CD5)</f>
         <v>0</v>
       </c>
       <c r="DP5">
-        <f>SUMIF(F2:DN2, DP1, F5:DN5)</f>
-        <v>0</v>
+        <f>SUMIF(H2:DN2, DP1, H5:DN5)</f>
+        <v>36</v>
       </c>
       <c r="DQ5">
-        <f>SUMIF(B2:CF2, DQ1, B5:CF5)</f>
         <v>0</v>
       </c>
       <c r="DR5">
-        <f>SUMIF(H2:DP2, DR1, H5:DP5)</f>
+        <f t="shared" ref="DR5:DR15" si="10">SUM(DJ5:DQ5)</f>
         <v>36</v>
       </c>
-      <c r="DS5">
+      <c r="DS5" s="11">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="DT5">
-        <f t="shared" ref="DT5:DT15" si="10">SUM(DL5:DS5)</f>
-        <v>36</v>
-      </c>
-      <c r="DU5" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="DU5">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DV5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="DW5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="DX5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="DY5">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="DZ5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA5">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="EB5">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC5" s="4">
+      <c r="EA5" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
@@ -2780,205 +2768,205 @@
         <f>(16000*0.08)/150</f>
         <v>8.5333333333333332</v>
       </c>
-      <c r="DK6" s="4">
+      <c r="DI6" s="4">
         <f t="shared" si="0"/>
         <v>213.66666666666666</v>
       </c>
-      <c r="DL6" s="11">
-        <f>SUMIF(B2:CF2, DL1, B6:CF6)</f>
+      <c r="DJ6" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B6:CD6)</f>
         <v>79</v>
       </c>
+      <c r="DK6">
+        <f>SUMIF(B2:CD2, DK1, B6:CD6)</f>
+        <v>0</v>
+      </c>
+      <c r="DL6">
+        <f>SUMIF(B2:CD2, DL1, B6:CD6)</f>
+        <v>106.66666666666667</v>
+      </c>
       <c r="DM6">
-        <f>SUMIF(B2:CF2, DM1, B6:CF6)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CD2, DM1, B6:CD6)</f>
+        <v>1</v>
       </c>
       <c r="DN6">
-        <f>SUMIF(B2:CF2, DN1, B6:CF6)</f>
-        <v>106.66666666666667</v>
+        <f>SUMIF(B2:CD2, DN1, B6:CD6)</f>
+        <v>27</v>
       </c>
       <c r="DO6">
-        <f>SUMIF(B2:CF2, DO1, B6:CF6)</f>
-        <v>1</v>
+        <f>SUMIF(B2:CD2, DO1, B6:CD6)</f>
+        <v>0</v>
       </c>
       <c r="DP6">
-        <f>SUMIF(B2:CF2, DP1, B6:CF6)</f>
-        <v>27</v>
+        <f>SUMIF(B2:CD2, DP1, B6:CD6)</f>
+        <v>0</v>
       </c>
       <c r="DQ6">
-        <f>SUMIF(B2:CF2, DQ1, B6:CF6)</f>
         <v>0</v>
       </c>
       <c r="DR6">
-        <f>SUMIF(B2:CF2, DR1, B6:CF6)</f>
-        <v>0</v>
-      </c>
-      <c r="DS6">
-        <v>0</v>
-      </c>
-      <c r="DT6">
         <f t="shared" si="10"/>
         <v>213.66666666666669</v>
       </c>
-      <c r="DU6" s="11">
+      <c r="DS6" s="11">
         <f t="shared" si="1"/>
         <v>0.36973478939157567</v>
       </c>
-      <c r="DV6">
+      <c r="DT6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="DW6">
+      <c r="DU6">
         <f t="shared" si="3"/>
         <v>0.49921996879875197</v>
       </c>
-      <c r="DX6">
+      <c r="DV6">
         <f t="shared" si="4"/>
         <v>4.6801872074882997E-3</v>
       </c>
-      <c r="DY6">
+      <c r="DW6">
         <f t="shared" si="5"/>
         <v>0.12636505460218408</v>
       </c>
+      <c r="DX6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="DY6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="DZ6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EB6">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC6" s="4">
+      <c r="EA6" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="Y7">
+      <c r="X7">
         <v>3</v>
       </c>
-      <c r="AQ7">
+      <c r="AO7">
         <v>5</v>
       </c>
-      <c r="BF7">
+      <c r="BD7">
         <v>5</v>
       </c>
-      <c r="BI7">
+      <c r="BG7">
         <v>7</v>
       </c>
+      <c r="BQ7">
+        <v>6</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
       <c r="BS7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BT7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BV7">
         <v>2</v>
       </c>
       <c r="BW7">
+        <v>2</v>
+      </c>
+      <c r="BX7">
+        <v>4</v>
+      </c>
+      <c r="BY7">
         <v>11</v>
       </c>
-      <c r="BX7">
-        <v>2</v>
-      </c>
-      <c r="BY7">
-        <v>2</v>
-      </c>
       <c r="BZ7">
-        <v>4</v>
-      </c>
-      <c r="CA7">
-        <v>11</v>
-      </c>
-      <c r="CB7">
         <v>17</v>
       </c>
-      <c r="DK7" s="4">
+      <c r="DI7" s="4">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="DL7" s="11">
-        <f>SUMIF(B2:CF2, DL1, B7:CF7)</f>
+      <c r="DJ7" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B7:CD7)</f>
         <v>46</v>
       </c>
+      <c r="DK7">
+        <f>SUMIF(B2:CD2, DK1, B7:CD7)</f>
+        <v>12</v>
+      </c>
+      <c r="DL7">
+        <f>SUMIF(B2:CD2, DL1, B7:CD7)</f>
+        <v>13</v>
+      </c>
       <c r="DM7">
-        <f>SUMIF(B2:CF2, DM1, B7:CF7)</f>
-        <v>12</v>
+        <f>SUMIF(B2:CD2, DM1, B7:CD7)</f>
+        <v>0</v>
       </c>
       <c r="DN7">
-        <f>SUMIF(B2:CF2, DN1, B7:CF7)</f>
-        <v>13</v>
+        <f>SUMIF(B2:CD2, DN1, B7:CD7)</f>
+        <v>0</v>
       </c>
       <c r="DO7">
-        <f>SUMIF(B2:CF2, DO1, B7:CF7)</f>
+        <f>SUMIF(B2:CD2, DO1, B7:CD7)</f>
         <v>0</v>
       </c>
       <c r="DP7">
-        <f>SUMIF(B2:CF2, DP1, B7:CF7)</f>
+        <f>SUMIF(B2:CD2, DP1, B7:CD7)</f>
         <v>0</v>
       </c>
       <c r="DQ7">
-        <f>SUMIF(B2:CF2, DQ1, B7:CF7)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="DR7">
-        <f>SUMIF(B2:CF2, DR1, B7:CF7)</f>
-        <v>0</v>
-      </c>
-      <c r="DS7">
-        <v>6</v>
-      </c>
-      <c r="DT7">
         <f t="shared" si="10"/>
         <v>77</v>
       </c>
-      <c r="DU7" s="11">
+      <c r="DS7" s="11">
         <f t="shared" si="1"/>
         <v>0.59740259740259738</v>
       </c>
-      <c r="DV7">
+      <c r="DT7">
         <f t="shared" si="2"/>
         <v>0.15584415584415584</v>
       </c>
-      <c r="DW7">
+      <c r="DU7">
         <f t="shared" si="3"/>
         <v>0.16883116883116883</v>
       </c>
+      <c r="DV7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="DW7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="DX7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="DY7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="DZ7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA7">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EB7">
         <f t="shared" si="8"/>
         <v>7.792207792207792E-2</v>
       </c>
-      <c r="EC7" s="4">
+      <c r="EA7" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -2995,379 +2983,376 @@
         <v>2</v>
       </c>
       <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>15</v>
+      </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>6</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
         <v>2</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
-        <v>15</v>
-      </c>
-      <c r="AA8">
-        <v>3</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-      <c r="AF8">
-        <v>6</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-      <c r="DK8" s="4">
+      <c r="DI8" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="DL8" s="11">
-        <f>SUMIF(B2:CF2, DL1, B8:CF8)</f>
-        <v>11</v>
+      <c r="DJ8" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B8:CD8)</f>
+        <v>13</v>
+      </c>
+      <c r="DK8">
+        <f>SUMIF(B2:CD2, DK1, B8:CD8)</f>
+        <v>17</v>
+      </c>
+      <c r="DL8">
+        <f>SUMIF(B2:CD2, DL1, B8:CD8)</f>
+        <v>0</v>
       </c>
       <c r="DM8">
-        <f>SUMIF(B2:CF2, DM1, B8:CF8)</f>
-        <v>17</v>
+        <f>SUMIF(B2:CD2, DM1, B8:CD8)</f>
+        <v>1</v>
       </c>
       <c r="DN8">
-        <f>SUMIF(B2:CF2, DN1, B8:CF8)</f>
-        <v>2</v>
+        <f>SUMIF(B2:CD2, DN1, B8:CD8)</f>
+        <v>0</v>
       </c>
       <c r="DO8">
-        <f>SUMIF(B2:CF2, DO1, B8:CF8)</f>
-        <v>1</v>
+        <f>SUMIF(B2:CD2, DO1, B8:CD8)</f>
+        <v>15</v>
       </c>
       <c r="DP8">
-        <f>SUMIF(B2:CF2, DP1, B8:CF8)</f>
+        <f>SUMIF(B2:CD2, DP1, B8:CD8)</f>
         <v>0</v>
       </c>
       <c r="DQ8">
-        <f>SUMIF(B2:CF2, DQ1, B8:CF8)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="DR8">
-        <f>SUMIF(B2:CF2, DR1, B8:CF8)</f>
-        <v>0</v>
-      </c>
-      <c r="DS8">
-        <v>0</v>
-      </c>
-      <c r="DT8">
         <f t="shared" si="10"/>
         <v>46</v>
       </c>
-      <c r="DU8" s="11">
+      <c r="DS8" s="11">
         <f t="shared" si="1"/>
-        <v>0.23404255319148937</v>
-      </c>
-      <c r="DV8">
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="DT8">
         <f t="shared" si="2"/>
         <v>0.36170212765957449</v>
       </c>
-      <c r="DW8">
+      <c r="DU8">
         <f t="shared" si="3"/>
-        <v>4.2553191489361701E-2</v>
-      </c>
-      <c r="DX8">
+        <v>0</v>
+      </c>
+      <c r="DV8">
         <f t="shared" si="4"/>
         <v>2.1276595744680851E-2</v>
       </c>
-      <c r="DY8">
+      <c r="DW8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DZ8">
+      <c r="DX8">
         <f t="shared" si="6"/>
         <v>0.31914893617021278</v>
       </c>
-      <c r="EA8">
+      <c r="DY8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="EB8">
+      <c r="DZ8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC8" s="4">
+      <c r="EA8" s="4">
         <f t="shared" si="9"/>
-        <v>0.97872340425531912</v>
+        <v>0.97872340425531923</v>
       </c>
     </row>
-    <row r="9" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
       <c r="AH9">
         <v>1</v>
       </c>
       <c r="AI9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK9">
         <v>3</v>
       </c>
       <c r="AL9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM9">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AN9">
         <v>1</v>
       </c>
       <c r="AO9">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="AQ9">
         <v>1</v>
       </c>
       <c r="AR9">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AS9">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AV9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW9">
-        <v>2</v>
-      </c>
-      <c r="AX9">
-        <v>5</v>
-      </c>
-      <c r="AY9">
-        <v>1</v>
-      </c>
-      <c r="DK9" s="4">
+        <v>1</v>
+      </c>
+      <c r="BH9">
+        <v>1</v>
+      </c>
+      <c r="DI9" s="4">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="DL9" s="11">
-        <f>SUMIF(B2:CF2, DL1, B9:CF9)</f>
-        <v>45</v>
+      <c r="DJ9" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B9:CD9)</f>
+        <v>15</v>
+      </c>
+      <c r="DK9">
+        <f>SUMIF(B2:CD2, DK1, B9:CD9)</f>
+        <v>1</v>
+      </c>
+      <c r="DL9">
+        <f>SUMIF(B2:CD2, DL1, B9:CD9)</f>
+        <v>48</v>
       </c>
       <c r="DM9">
-        <f>SUMIF(B2:CF2, DM1, B9:CF9)</f>
-        <v>1</v>
+        <f>SUMIF(B2:CD2, DM1, B9:CD9)</f>
+        <v>0</v>
       </c>
       <c r="DN9">
-        <f>SUMIF(B2:CF2, DN1, B9:CF9)</f>
-        <v>48</v>
+        <f>SUMIF(B2:CD2, DN1, B9:CD9)</f>
+        <v>0</v>
       </c>
       <c r="DO9">
-        <f>SUMIF(B2:CF2, DO1, B9:CF9)</f>
+        <f>SUMIF(B2:CD2, DO1, B9:CD9)</f>
         <v>0</v>
       </c>
       <c r="DP9">
-        <f>SUMIF(B2:CF2, DP1, B9:CF9)</f>
+        <f>SUMIF(B2:CD2, DP1, B9:CD9)</f>
         <v>0</v>
       </c>
       <c r="DQ9">
-        <f>SUMIF(B2:CF2, DQ1, B9:CF9)</f>
         <v>0</v>
       </c>
       <c r="DR9">
-        <f>SUMIF(B2:CF2, DR1, B9:CF9)</f>
-        <v>0</v>
-      </c>
-      <c r="DS9">
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>64</v>
+      </c>
+      <c r="DS9" s="11">
+        <f t="shared" si="1"/>
+        <v>0.15957446808510639</v>
       </c>
       <c r="DT9">
-        <f t="shared" si="10"/>
-        <v>94</v>
-      </c>
-      <c r="DU9" s="11">
-        <f t="shared" si="1"/>
-        <v>0.47872340425531917</v>
-      </c>
-      <c r="DV9">
         <f t="shared" si="2"/>
         <v>1.0638297872340425E-2</v>
       </c>
-      <c r="DW9">
+      <c r="DU9">
         <f t="shared" si="3"/>
         <v>0.51063829787234039</v>
       </c>
+      <c r="DV9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="DW9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="DX9">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="DY9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="DZ9">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="EA9" s="4">
+        <f t="shared" si="9"/>
+        <v>0.68085106382978722</v>
+      </c>
+    </row>
+    <row r="10" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE10">
+        <v>7</v>
+      </c>
+      <c r="AJ10">
+        <v>15</v>
+      </c>
+      <c r="AX10">
+        <v>8</v>
+      </c>
+      <c r="AY10">
+        <v>7</v>
+      </c>
+      <c r="AZ10">
+        <v>1</v>
+      </c>
+      <c r="BA10">
+        <v>5</v>
+      </c>
+      <c r="BB10">
+        <v>15</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
+        <v>9</v>
+      </c>
+      <c r="BE10">
+        <v>4</v>
+      </c>
+      <c r="BF10">
+        <v>7</v>
+      </c>
+      <c r="BG10">
+        <v>2</v>
+      </c>
+      <c r="BH10">
+        <v>20</v>
+      </c>
+      <c r="BI10">
+        <v>1</v>
+      </c>
+      <c r="DI10" s="4">
+        <f t="shared" si="0"/>
+        <v>112</v>
+      </c>
+      <c r="DJ10" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B10:CD10)</f>
+        <v>47</v>
+      </c>
+      <c r="DK10">
+        <f>SUMIF(B2:CD2, DK1, B10:CD10)</f>
+        <v>14</v>
+      </c>
+      <c r="DL10">
+        <f>SUMIF(B2:CD2, DL1, B10:CD10)</f>
+        <v>51</v>
+      </c>
+      <c r="DM10">
+        <f>SUMIF(B2:CD2, DM1, B10:CD10)</f>
+        <v>0</v>
+      </c>
+      <c r="DN10">
+        <f>SUMIF(B2:CD2, DN1, B10:CD10)</f>
+        <v>0</v>
+      </c>
+      <c r="DO10">
+        <f>SUMIF(B2:CD2, DO1, B10:CD10)</f>
+        <v>0</v>
+      </c>
+      <c r="DP10">
+        <f>SUMIF(B2:CD2, DP1, B10:CD10)</f>
+        <v>0</v>
+      </c>
+      <c r="DQ10">
+        <v>0</v>
+      </c>
+      <c r="DR10">
+        <f t="shared" si="10"/>
+        <v>112</v>
+      </c>
+      <c r="DS10" s="11">
+        <f t="shared" si="1"/>
+        <v>0.41964285714285715</v>
+      </c>
+      <c r="DT10">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="DU10">
+        <f t="shared" si="3"/>
+        <v>0.45535714285714285</v>
+      </c>
+      <c r="DV10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="DY9">
+      <c r="DW10">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DZ9">
+      <c r="DX10">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="EA9">
+      <c r="DY10">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="EB9">
+      <c r="DZ10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC9" s="4">
+      <c r="EA10" s="4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:135" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="11" spans="1:133" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="AF10">
-        <v>7</v>
-      </c>
-      <c r="AI10">
-        <v>20</v>
-      </c>
-      <c r="AL10">
-        <v>15</v>
-      </c>
-      <c r="AZ10">
-        <v>8</v>
-      </c>
-      <c r="BA10">
-        <v>7</v>
-      </c>
-      <c r="BB10">
-        <v>1</v>
-      </c>
-      <c r="BC10">
-        <v>5</v>
-      </c>
-      <c r="BD10">
-        <v>15</v>
-      </c>
-      <c r="BE10">
-        <v>11</v>
-      </c>
-      <c r="BF10">
-        <v>9</v>
-      </c>
-      <c r="BG10">
-        <v>4</v>
-      </c>
-      <c r="BH10">
-        <v>7</v>
-      </c>
-      <c r="BI10">
-        <v>2</v>
-      </c>
-      <c r="BJ10">
-        <v>1</v>
-      </c>
-      <c r="BK10">
-        <v>1</v>
-      </c>
-      <c r="DK10" s="4">
-        <f t="shared" si="0"/>
-        <v>113</v>
-      </c>
-      <c r="DL10" s="11">
-        <f>SUMIF(B2:CF2, DL1, B10:CF10)</f>
-        <v>47</v>
-      </c>
-      <c r="DM10">
-        <f>SUMIF(B2:CF2, DM1, B10:CF10)</f>
-        <v>14</v>
-      </c>
-      <c r="DN10">
-        <f>SUMIF(B2:CF2, DN1, B10:CF10)</f>
-        <v>52</v>
-      </c>
-      <c r="DO10">
-        <f>SUMIF(B2:CF2, DO1, B10:CF10)</f>
-        <v>0</v>
-      </c>
-      <c r="DP10">
-        <f>SUMIF(B2:CF2, DP1, B10:CF10)</f>
-        <v>0</v>
-      </c>
-      <c r="DQ10">
-        <f>SUMIF(B2:CF2, DQ1, B10:CF10)</f>
-        <v>0</v>
-      </c>
-      <c r="DR10">
-        <f>SUMIF(B2:CF2, DR1, B10:CF10)</f>
-        <v>0</v>
-      </c>
-      <c r="DS10">
-        <v>0</v>
-      </c>
-      <c r="DT10">
-        <f t="shared" si="10"/>
-        <v>113</v>
-      </c>
-      <c r="DU10" s="11">
-        <f t="shared" si="1"/>
-        <v>0.41592920353982299</v>
-      </c>
-      <c r="DV10">
-        <f t="shared" si="2"/>
-        <v>0.12389380530973451</v>
-      </c>
-      <c r="DW10">
-        <f t="shared" si="3"/>
-        <v>0.46017699115044247</v>
-      </c>
-      <c r="DX10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="DY10">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="DZ10">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA10">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EB10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="EC10" s="4">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:135" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -3379,332 +3364,332 @@
         <f>64/3</f>
         <v>21.333333333333332</v>
       </c>
-      <c r="AM11">
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="BJ11">
+        <v>4</v>
+      </c>
+      <c r="BK11">
         <v>1</v>
       </c>
       <c r="BL11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BM11">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="BN11">
         <v>1</v>
       </c>
       <c r="BO11">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="BP11">
-        <v>1</v>
-      </c>
-      <c r="BQ11">
-        <v>1</v>
-      </c>
-      <c r="BR11">
         <v>15</v>
       </c>
-      <c r="DK11" s="4">
+      <c r="DI11" s="4">
         <f t="shared" si="0"/>
         <v>77.333333333333329</v>
       </c>
-      <c r="DL11" s="11">
-        <f>SUMIF(B2:CF2, DL1, B11:CF11)</f>
+      <c r="DJ11" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B11:CD11)</f>
         <v>20</v>
       </c>
+      <c r="DK11">
+        <f>SUMIF(B2:CD2, DK1, B11:CD11)</f>
+        <v>0</v>
+      </c>
+      <c r="DL11">
+        <f>SUMIF(B2:CD2, DL1, B11:CD11)</f>
+        <v>41.333333333333329</v>
+      </c>
       <c r="DM11">
-        <f>SUMIF(B2:CF2, DM1, B11:CF11)</f>
+        <f>SUMIF(B2:CD2, DM1, B11:CD11)</f>
         <v>0</v>
       </c>
       <c r="DN11">
-        <f>SUMIF(B2:CF2, DN1, B11:CF11)</f>
-        <v>41.333333333333329</v>
+        <f>SUMIF(B2:CD2, DN1, B11:CD11)</f>
+        <v>0</v>
       </c>
       <c r="DO11">
-        <f>SUMIF(B2:CF2, DO1, B11:CF11)</f>
+        <f>SUMIF(B2:CD2, DO1, B11:CD11)</f>
         <v>0</v>
       </c>
       <c r="DP11">
-        <f>SUMIF(B2:CF2, DP1, B11:CF11)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CD2, DP1, B11:CD11)</f>
+        <v>15</v>
       </c>
       <c r="DQ11">
-        <f>SUMIF(B2:CF2, DQ1, B11:CF11)</f>
         <v>0</v>
       </c>
       <c r="DR11">
-        <f>SUMIF(B2:CF2, DR1, B11:CF11)</f>
-        <v>15</v>
-      </c>
-      <c r="DS11">
-        <v>0</v>
-      </c>
-      <c r="DT11">
         <f t="shared" si="10"/>
         <v>76.333333333333329</v>
       </c>
-      <c r="DU11" s="11">
+      <c r="DS11" s="11">
         <f t="shared" si="1"/>
         <v>0.25862068965517243</v>
       </c>
-      <c r="DV11">
+      <c r="DT11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="DW11">
+      <c r="DU11">
         <f t="shared" si="3"/>
         <v>0.53448275862068961</v>
       </c>
+      <c r="DV11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="DW11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="DX11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="DY11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="DZ11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA11">
         <f t="shared" si="7"/>
         <v>0.19396551724137931</v>
       </c>
-      <c r="EB11">
+      <c r="DZ11">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC11" s="4">
+      <c r="EA11" s="4">
         <f t="shared" si="9"/>
         <v>0.98706896551724144</v>
       </c>
     </row>
-    <row r="12" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="CA12">
+        <v>5</v>
+      </c>
+      <c r="CB12">
+        <v>4</v>
       </c>
       <c r="CC12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CD12">
-        <v>4</v>
-      </c>
-      <c r="CE12">
-        <v>1</v>
-      </c>
-      <c r="CF12">
         <v>2</v>
       </c>
-      <c r="DK12" s="4">
+      <c r="DI12" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="DL12" s="11">
-        <f>SUMIF(B2:CF2, DL1, B12:CF12)</f>
+      <c r="DJ12" s="11">
+        <f>SUMIF(B2:CD2, DJ1, B12:CD12)</f>
+        <v>0</v>
+      </c>
+      <c r="DK12">
+        <f>SUMIF(B2:CD2, DK1, B12:CD15)</f>
+        <v>0</v>
+      </c>
+      <c r="DL12">
+        <f>SUMIF(B2:CD2, DL1, B12:CD15)</f>
         <v>0</v>
       </c>
       <c r="DM12">
-        <f>SUMIF(B2:CF2, DM1, B12:CF15)</f>
-        <v>0</v>
+        <f>SUMIF(B2:CD2, DM1, B12:CD12)</f>
+        <v>10</v>
       </c>
       <c r="DN12">
-        <f>SUMIF(B2:CF2, DN1, B12:CF15)</f>
+        <f>SUMIF(B2:CD2, DN1, B12:CD15)</f>
         <v>0</v>
       </c>
       <c r="DO12">
-        <f>SUMIF(B2:CF2, DO1, B12:CF12)</f>
-        <v>10</v>
+        <f>SUMIF(B2:CD2, DO1, B12:CD15)</f>
+        <v>0</v>
       </c>
       <c r="DP12">
-        <f>SUMIF(B2:CF2, DP1, B12:CF15)</f>
+        <f>SUMIF(B2:CD2, DP1, B12:CD15)</f>
         <v>0</v>
       </c>
       <c r="DQ12">
-        <f>SUMIF(B2:CF2, DQ1, B12:CF15)</f>
         <v>0</v>
       </c>
       <c r="DR12">
-        <f>SUMIF(B2:CF2, DR1, B12:CF15)</f>
-        <v>0</v>
-      </c>
-      <c r="DS12">
-        <v>0</v>
-      </c>
-      <c r="DT12">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="DU12" s="11">
+      <c r="DS12" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="DT12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="DU12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="DV12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="DW12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="DX12">
         <f t="shared" si="4"/>
         <v>0.83333333333333337</v>
       </c>
+      <c r="DW12">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="DX12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="DY12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="DZ12">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="EA12">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="EB12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="EC12" s="4">
+      <c r="EA12" s="4">
         <f t="shared" si="9"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="CE13">
+        <v>8</v>
+      </c>
+      <c r="CF13">
+        <v>6</v>
       </c>
       <c r="CG13">
         <v>8</v>
       </c>
       <c r="CH13">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="CI13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CJ13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CK13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CL13">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="CM13">
+        <v>2</v>
+      </c>
+      <c r="CN13">
+        <v>13</v>
+      </c>
+      <c r="CO13">
+        <v>9</v>
+      </c>
+      <c r="CP13">
+        <v>4</v>
+      </c>
+      <c r="CQ13">
+        <v>4</v>
+      </c>
+      <c r="CR13">
+        <v>2</v>
+      </c>
+      <c r="CS13">
+        <v>2</v>
+      </c>
+      <c r="CT13">
+        <v>1</v>
+      </c>
+      <c r="CU13">
+        <v>3</v>
+      </c>
+      <c r="CV13">
         <v>5</v>
       </c>
-      <c r="CN13">
-        <v>26</v>
-      </c>
-      <c r="CO13">
-        <v>2</v>
-      </c>
-      <c r="CP13">
-        <v>13</v>
-      </c>
-      <c r="CQ13">
-        <v>9</v>
-      </c>
-      <c r="CR13">
-        <v>4</v>
-      </c>
-      <c r="CS13">
-        <v>4</v>
-      </c>
-      <c r="CT13">
-        <v>2</v>
-      </c>
-      <c r="CU13">
-        <v>2</v>
-      </c>
-      <c r="CV13">
-        <v>1</v>
-      </c>
-      <c r="CW13">
-        <v>3</v>
-      </c>
-      <c r="CX13">
-        <v>5</v>
-      </c>
-      <c r="DK13" s="4">
-        <f>SUM(B13:CY13)</f>
+      <c r="DI13" s="4">
+        <f>SUM(B13:CW13)</f>
         <v>145</v>
       </c>
+      <c r="DJ13">
+        <f>SUMIF(B2:DH2, DJ1, B13:DH13)</f>
+        <v>75</v>
+      </c>
+      <c r="DK13">
+        <f>SUMIF(B2:DH2, DK1, B13:DH13)</f>
+        <v>19</v>
+      </c>
       <c r="DL13">
-        <f>SUMIF(B2:DJ2, DL1, B13:DJ13)</f>
-        <v>86</v>
+        <f>SUMIF(B2:DH2, DL1, B13:DH13)</f>
+        <v>49</v>
       </c>
       <c r="DM13">
-        <f>SUMIF(B2:DJ2, DM1, B13:DJ13)</f>
-        <v>8</v>
+        <f>SUMIF(B2:DH2, DM1, B13:DH13)</f>
+        <v>0</v>
       </c>
       <c r="DN13">
-        <f>SUMIF(B2:DJ2, DN1, B13:DJ13)</f>
-        <v>49</v>
+        <f>SUMIF(B2:DH2, DN1, B13:DH13)</f>
+        <v>0</v>
       </c>
       <c r="DO13">
-        <f>SUMIF(B2:DJ2, DO1, B13:DJ13)</f>
+        <f>SUMIF(B2:DH2, DO1, B13:DH13)</f>
         <v>0</v>
       </c>
       <c r="DP13">
-        <f>SUMIF(B2:DJ2, DP1, B13:DJ13)</f>
         <v>0</v>
       </c>
       <c r="DQ13">
-        <f>SUMIF(B2:DJ2, DQ1, B13:DJ13)</f>
         <v>0</v>
       </c>
       <c r="DR13">
-        <v>0</v>
-      </c>
-      <c r="DS13">
-        <v>0</v>
-      </c>
-      <c r="DT13">
         <f t="shared" si="10"/>
         <v>143</v>
       </c>
-      <c r="DU13" s="11">
+      <c r="DS13" s="11">
         <f t="shared" si="1"/>
-        <v>0.59310344827586203</v>
-      </c>
-      <c r="DV13">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="DT13">
         <f t="shared" si="2"/>
-        <v>5.5172413793103448E-2</v>
-      </c>
-      <c r="DW13">
+        <v>0.1310344827586207</v>
+      </c>
+      <c r="DU13">
         <f t="shared" si="3"/>
         <v>0.33793103448275863</v>
       </c>
-      <c r="DX13" s="11">
+      <c r="DV13" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="DY13">
-        <f t="shared" ref="DY13" si="11">DP13/DN13</f>
+      <c r="DW13">
+        <f t="shared" ref="DW13" si="11">DN13/DL13</f>
+        <v>0</v>
+      </c>
+      <c r="DX13">
+        <f t="shared" ref="DX13:DX14" si="12">DO13/DL13</f>
+        <v>0</v>
+      </c>
+      <c r="DY13" s="11">
         <v>0</v>
       </c>
       <c r="DZ13">
-        <f t="shared" ref="DZ13:DZ14" si="12">DQ13/DN13</f>
-        <v>0</v>
-      </c>
-      <c r="EA13" s="11">
-        <v>0</v>
-      </c>
-      <c r="EB13">
-        <v>0</v>
-      </c>
-      <c r="EC13" s="4">
+        <v>0</v>
+      </c>
+      <c r="EA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.98620689655172411</v>
+        <v>0.98620689655172422</v>
       </c>
     </row>
-    <row r="14" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:133" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q14">
         <f>(16000*0.3)/150</f>
@@ -3713,123 +3698,123 @@
       <c r="S14">
         <v>2</v>
       </c>
-      <c r="CR14">
+      <c r="CP14">
         <v>6</v>
+      </c>
+      <c r="CW14">
+        <v>2</v>
+      </c>
+      <c r="CX14">
+        <v>9</v>
       </c>
       <c r="CY14">
         <v>2</v>
       </c>
       <c r="CZ14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="DA14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="DB14">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="DC14">
-        <v>20</v>
-      </c>
-      <c r="DD14">
-        <v>40</v>
-      </c>
-      <c r="DE14">
         <f>(16000*0.3)/400</f>
         <v>12</v>
       </c>
+      <c r="DD14">
+        <v>15</v>
+      </c>
+      <c r="DE14">
+        <v>1</v>
+      </c>
       <c r="DF14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="DG14">
         <v>1</v>
       </c>
       <c r="DH14">
+        <v>23</v>
+      </c>
+      <c r="DI14" s="4">
+        <f>SUM(B14:DH14)</f>
+        <v>175</v>
+      </c>
+      <c r="DJ14">
+        <f ca="1">SUMIF(B2:DH2, DJ1, B14:CD14)</f>
+        <v>40</v>
+      </c>
+      <c r="DK14">
+        <f ca="1">SUMIF(B2:DH2, DK1, B14:CD14)</f>
         <v>5</v>
       </c>
-      <c r="DI14">
-        <v>1</v>
-      </c>
-      <c r="DJ14">
-        <v>23</v>
-      </c>
-      <c r="DK14" s="4">
-        <f>SUM(B14:DJ14)</f>
-        <v>175</v>
-      </c>
       <c r="DL14">
-        <f ca="1">SUMIF(B2:DJ2, DL1, B14:CF14)</f>
-        <v>40</v>
+        <f ca="1">SUMIF(B2:DH2, DL1, B14:CD14)</f>
+        <v>99</v>
       </c>
       <c r="DM14">
-        <f ca="1">SUMIF(B2:DJ2, DM1, B14:CF14)</f>
-        <v>5</v>
+        <f ca="1">SUMIF(B2:DH2, DM1, B14:CD14)</f>
+        <v>2</v>
       </c>
       <c r="DN14">
-        <f ca="1">SUMIF(B2:DJ2, DN1, B14:CF14)</f>
-        <v>99</v>
+        <f ca="1">SUMIF(B2:DH2, DN1, B14:CD14)</f>
+        <v>0</v>
       </c>
       <c r="DO14">
-        <f ca="1">SUMIF(B2:DJ2, DO1, B14:CF14)</f>
-        <v>2</v>
+        <f ca="1">SUMIF(B2:DH2, DO1, B14:CD14)</f>
+        <v>0</v>
       </c>
       <c r="DP14">
-        <f ca="1">SUMIF(B2:DJ2, DP1, B14:CF14)</f>
+        <f ca="1">SUMIF(B2:DH2, DP1, B14:CD14)</f>
         <v>0</v>
       </c>
       <c r="DQ14">
-        <f ca="1">SUMIF(B2:DJ2, DQ1, B14:CF14)</f>
         <v>0</v>
       </c>
       <c r="DR14">
-        <f ca="1">SUMIF(B2:DJ2, DR1, B14:CF14)</f>
-        <v>0</v>
-      </c>
-      <c r="DS14">
-        <v>0</v>
-      </c>
-      <c r="DT14">
         <f t="shared" ca="1" si="10"/>
         <v>146</v>
       </c>
-      <c r="DU14" s="11">
+      <c r="DS14" s="11">
         <f t="shared" ca="1" si="1"/>
         <v>0.22857142857142856</v>
       </c>
-      <c r="DV14">
+      <c r="DT14">
         <f t="shared" ca="1" si="2"/>
         <v>2.8571428571428571E-2</v>
       </c>
-      <c r="DW14">
+      <c r="DU14">
         <f t="shared" ca="1" si="3"/>
         <v>0.56571428571428573</v>
       </c>
-      <c r="DX14" s="11">
+      <c r="DV14" s="11">
         <f t="shared" ca="1" si="4"/>
         <v>1.1428571428571429E-2</v>
       </c>
-      <c r="DY14">
-        <f ca="1">DP14/DK14</f>
+      <c r="DW14">
+        <f ca="1">DN14/DI14</f>
+        <v>0</v>
+      </c>
+      <c r="DX14">
+        <f t="shared" ca="1" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="DY14" s="11">
         <v>0</v>
       </c>
       <c r="DZ14">
-        <f t="shared" ca="1" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="EA14" s="11">
-        <v>0</v>
-      </c>
-      <c r="EB14">
-        <v>0</v>
-      </c>
-      <c r="EC14" s="4">
+        <v>0</v>
+      </c>
+      <c r="EA14" s="4">
         <f t="shared" ca="1" si="9"/>
         <v>0.8342857142857143</v>
       </c>
     </row>
-    <row r="15" spans="1:135" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:133" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1">
         <f>SUM(B3:B14)</f>
@@ -3840,7 +3825,7 @@
         <v>41</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" ref="D15:BN15" si="13">SUM(D3:D14)</f>
+        <f t="shared" ref="D15:BL15" si="13">SUM(D3:D14)</f>
         <v>28</v>
       </c>
       <c r="E15" s="1">
@@ -3917,452 +3902,444 @@
       </c>
       <c r="W15" s="1">
         <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="Y15" s="1">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="Z15" s="1">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AA15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AB15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AE15" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AH15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AI15" s="1">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="AJ15" s="1">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="AK15" s="1">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AL15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AM15" s="1">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="AN15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AO15" s="1">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="AP15" s="1">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="AQ15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AR15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AS15" s="1">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="AT15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AU15" s="1">
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="X15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="Y15" s="1">
+      <c r="AV15" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="AW15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="AX15" s="1">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="AY15" s="1">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="AZ15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BA15" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="BB15" s="1">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="BD15" s="1">
+        <f t="shared" si="13"/>
+        <v>14</v>
+      </c>
+      <c r="BE15" s="1">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="Z15" s="1">
-        <f t="shared" si="13"/>
+      <c r="BF15" s="1">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="BH15" s="1">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="BI15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BJ15" s="1">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="BK15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BL15" s="1">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" ref="BM15:DY15" si="14">SUM(BM3:BM14)</f>
+        <v>14</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="AA15" s="1">
-        <f t="shared" si="13"/>
+      <c r="BQ15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="14"/>
+        <v>17</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="14"/>
+        <v>24</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" si="14"/>
+        <v>11</v>
+      </c>
+      <c r="CJ15" s="1">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="CK15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CL15" s="1">
+        <f t="shared" si="14"/>
+        <v>26</v>
+      </c>
+      <c r="CM15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="AB15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AC15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AD15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AE15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AF15" s="1">
-        <f t="shared" si="13"/>
-        <v>13</v>
-      </c>
-      <c r="AG15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AH15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AI15" s="1">
-        <f t="shared" si="13"/>
-        <v>21</v>
-      </c>
-      <c r="AJ15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AK15" s="1">
-        <f t="shared" si="13"/>
-        <v>3</v>
-      </c>
-      <c r="AL15" s="1">
-        <f t="shared" si="13"/>
-        <v>18</v>
-      </c>
-      <c r="AM15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="AN15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AO15" s="1">
-        <f t="shared" si="13"/>
-        <v>30</v>
-      </c>
-      <c r="AP15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AQ15" s="1">
-        <f t="shared" si="13"/>
-        <v>6</v>
-      </c>
-      <c r="AR15" s="1">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="AS15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AT15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AU15" s="1">
-        <f t="shared" si="13"/>
-        <v>13</v>
-      </c>
-      <c r="AV15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AW15" s="1">
-        <f t="shared" si="13"/>
+      <c r="CV15" s="1">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="AX15" s="1">
-        <f t="shared" si="13"/>
+      <c r="CX15" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="AY15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="AZ15" s="1">
-        <f t="shared" si="13"/>
-        <v>8</v>
-      </c>
-      <c r="BA15" s="1">
-        <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="BB15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BC15" s="1">
-        <f t="shared" si="13"/>
+      <c r="DA15" s="1">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" si="14"/>
+        <v>40</v>
+      </c>
+      <c r="DC15" s="1">
+        <f t="shared" si="14"/>
+        <v>12</v>
+      </c>
+      <c r="DD15" s="1">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="DE15" s="1">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="DF15" s="1">
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="BD15" s="1">
-        <f t="shared" si="13"/>
-        <v>15</v>
-      </c>
-      <c r="BE15" s="1">
-        <f t="shared" si="13"/>
-        <v>11</v>
-      </c>
-      <c r="BF15" s="1">
-        <f t="shared" si="13"/>
-        <v>14</v>
-      </c>
-      <c r="BG15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="BH15" s="1">
-        <f t="shared" si="13"/>
-        <v>7</v>
-      </c>
-      <c r="BI15" s="1">
-        <f t="shared" si="13"/>
-        <v>9</v>
-      </c>
-      <c r="BJ15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BK15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BL15" s="1">
-        <f t="shared" si="13"/>
-        <v>4</v>
-      </c>
-      <c r="BM15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BN15" s="1">
-        <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="BO15" s="1">
-        <f t="shared" ref="BO15:EA15" si="14">SUM(BO3:BO14)</f>
-        <v>14</v>
-      </c>
-      <c r="BP15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BQ15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BR15" s="1">
-        <f t="shared" si="14"/>
-        <v>15</v>
-      </c>
-      <c r="BS15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="BT15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BU15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="BV15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="BW15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="BX15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="BY15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="BZ15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CA15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="CB15" s="1">
-        <f t="shared" si="14"/>
-        <v>17</v>
-      </c>
-      <c r="CC15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CD15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CE15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="CF15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CG15" s="1">
-        <f t="shared" si="14"/>
-        <v>8</v>
-      </c>
-      <c r="CH15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" si="14"/>
-        <v>8</v>
-      </c>
-      <c r="CJ15" s="1">
-        <f t="shared" si="14"/>
-        <v>24</v>
-      </c>
-      <c r="CK15" s="1">
-        <f t="shared" si="14"/>
-        <v>11</v>
-      </c>
-      <c r="CL15" s="1">
-        <f t="shared" si="14"/>
-        <v>12</v>
-      </c>
-      <c r="CM15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CN15" s="1">
-        <f t="shared" si="14"/>
-        <v>26</v>
-      </c>
-      <c r="CO15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CP15" s="1">
-        <f t="shared" si="14"/>
-        <v>13</v>
-      </c>
-      <c r="CQ15" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="CR15" s="1">
-        <f t="shared" si="14"/>
-        <v>10</v>
-      </c>
-      <c r="CS15" s="1">
-        <f t="shared" si="14"/>
-        <v>4</v>
-      </c>
-      <c r="CT15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CU15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CV15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="CW15" s="1">
-        <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="CX15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="CY15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="14"/>
-        <v>2</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="14"/>
-        <v>20</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="14"/>
-        <v>40</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="14"/>
-        <v>12</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="14"/>
-        <v>15</v>
-      </c>
       <c r="DG15" s="1">
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="DH15" s="1">
         <f t="shared" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="DI15" s="1">
-        <f t="shared" si="14"/>
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="DI15" s="5">
+        <f t="shared" si="14"/>
+        <v>1146.1333333333332</v>
       </c>
       <c r="DJ15" s="1">
-        <f t="shared" si="14"/>
-        <v>23</v>
-      </c>
-      <c r="DK15" s="5">
-        <f t="shared" si="14"/>
-        <v>1147.1333333333332</v>
+        <f t="shared" ca="1" si="14"/>
+        <v>453</v>
+      </c>
+      <c r="DK15" s="1">
+        <f t="shared" ca="1" si="14"/>
+        <v>68</v>
       </c>
       <c r="DL15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="DM15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="DN15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>447</v>
+        <v>29.133333333333333</v>
       </c>
       <c r="DO15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>29.133333333333333</v>
+        <v>53.133333333333333</v>
       </c>
       <c r="DQ15" s="1">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="DR15" s="15">
+        <f t="shared" ca="1" si="10"/>
+        <v>1082.2666666666667</v>
+      </c>
+      <c r="DS15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>15</v>
-      </c>
-      <c r="DR15" s="1">
+        <v>4.3937979109245564</v>
+      </c>
+      <c r="DT15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>53.133333333333333</v>
-      </c>
-      <c r="DS15" s="1">
-        <f t="shared" si="14"/>
-        <v>6</v>
-      </c>
-      <c r="DT15" s="15">
-        <f t="shared" ca="1" si="10"/>
-        <v>1113.2666666666669</v>
+        <v>0.81279049270612003</v>
       </c>
       <c r="DU15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>4.7425420709678905</v>
+        <v>3.4713788424091212</v>
       </c>
       <c r="DV15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.73582222905033723</v>
+        <v>0.87071868771407401</v>
       </c>
       <c r="DW15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>3.5187518821917827</v>
+        <v>0.14977397925470787</v>
       </c>
       <c r="DX15" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.87071868771407401</v>
+        <v>0.31914893617021278</v>
       </c>
       <c r="DY15" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.14977397925470787</v>
+        <f t="shared" si="14"/>
+        <v>1.217374441893903</v>
       </c>
       <c r="DZ15" s="1">
-        <f t="shared" ca="1" si="14"/>
-        <v>0.31914893617021278</v>
-      </c>
-      <c r="EA15" s="1">
-        <f t="shared" si="14"/>
-        <v>1.217374441893903</v>
-      </c>
-      <c r="EB15" s="1">
-        <f t="shared" ref="EB15:EC15" si="15">SUM(EB3:EB14)</f>
+        <f t="shared" ref="DZ15:EA15" si="15">SUM(DZ3:DZ14)</f>
         <v>7.792207792207792E-2</v>
       </c>
-      <c r="EC15" s="15">
+      <c r="EA15" s="15">
         <f t="shared" ca="1" si="15"/>
-        <v>11.632054305164987</v>
-      </c>
-      <c r="ED15"/>
-      <c r="EE15"/>
+        <v>11.312905368994775</v>
+      </c>
+      <c r="EB15"/>
+      <c r="EC15"/>
     </row>
-    <row r="16" spans="1:135" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:133" x14ac:dyDescent="0.2">
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="H16" s="12"/>
@@ -4371,7 +4348,8 @@
       <c r="N16" s="12"/>
       <c r="O16" s="12"/>
       <c r="T16" s="12"/>
-      <c r="X16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="Z16" s="12"/>
       <c r="AA16" s="12"/>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
@@ -4387,30 +4365,28 @@
       <c r="AM16" s="12"/>
       <c r="AN16" s="12"/>
       <c r="AO16" s="12"/>
-      <c r="AP16" s="12"/>
       <c r="AQ16" s="12"/>
       <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
       <c r="AU16" s="12"/>
       <c r="AV16" s="12"/>
       <c r="AW16" s="12"/>
-      <c r="AX16" s="12"/>
       <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
       <c r="BA16" s="12"/>
       <c r="BB16" s="12"/>
       <c r="BC16" s="12"/>
-      <c r="BD16" s="12"/>
       <c r="BE16" s="12"/>
       <c r="BG16" s="12"/>
       <c r="BI16" s="12"/>
+      <c r="BJ16" s="12"/>
       <c r="BK16" s="12"/>
       <c r="BL16" s="12"/>
       <c r="BM16" s="12"/>
       <c r="BN16" s="12"/>
-      <c r="BO16" s="12"/>
-      <c r="BP16" s="12"/>
-      <c r="BS16" s="12"/>
-      <c r="BV16" s="12"/>
-      <c r="CA16" s="12"/>
+      <c r="BQ16" s="12"/>
+      <c r="BT16" s="12"/>
+      <c r="BY16" s="12"/>
     </row>
     <row r="22" spans="7:8" x14ac:dyDescent="0.2">
       <c r="G22" s="12"/>
@@ -4428,19 +4404,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -4490,7 +4466,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>0.05</v>
